--- a/automation/reports/Excel/Validation_Testing_Report.xlsx
+++ b/automation/reports/Excel/Validation_Testing_Report.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05 19:40:03</t>
+          <t>2026-10-05 21:16:36</t>
         </is>
       </c>
     </row>
@@ -735,7 +735,7 @@
       </c>
       <c r="E16" s="10" t="inlineStr">
         <is>
-          <t>78.93s</t>
+          <t>83.09s</t>
         </is>
       </c>
     </row>
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="H2" s="11" t="n">
-        <v>0.18</v>
+        <v>0.26</v>
       </c>
       <c r="I2" s="11" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         </is>
       </c>
       <c r="H3" s="14" t="n">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="I3" s="14" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         </is>
       </c>
       <c r="H4" s="11" t="n">
-        <v>0.36</v>
+        <v>0.41</v>
       </c>
       <c r="I4" s="11" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         </is>
       </c>
       <c r="H5" s="14" t="n">
-        <v>0.39</v>
+        <v>0.16</v>
       </c>
       <c r="I5" s="14" t="inlineStr">
         <is>
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="H6" s="11" t="n">
-        <v>0.14</v>
+        <v>0.09</v>
       </c>
       <c r="I6" s="11" t="inlineStr">
         <is>
@@ -1157,7 +1157,7 @@
         </is>
       </c>
       <c r="H8" s="11" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.17</v>
       </c>
       <c r="I8" s="11" t="inlineStr">
         <is>
@@ -1207,7 +1207,7 @@
         </is>
       </c>
       <c r="H9" s="14" t="n">
-        <v>0.32</v>
+        <v>0.11</v>
       </c>
       <c r="I9" s="14" t="inlineStr">
         <is>
@@ -1257,7 +1257,7 @@
         </is>
       </c>
       <c r="H10" s="11" t="n">
-        <v>0.1</v>
+        <v>0.31</v>
       </c>
       <c r="I10" s="11" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         </is>
       </c>
       <c r="H11" s="14" t="n">
-        <v>0.27</v>
+        <v>0.12</v>
       </c>
       <c r="I11" s="14" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         </is>
       </c>
       <c r="H12" s="11" t="n">
-        <v>0.18</v>
+        <v>0.39</v>
       </c>
       <c r="I12" s="11" t="inlineStr">
         <is>
@@ -1407,7 +1407,7 @@
         </is>
       </c>
       <c r="H13" s="14" t="n">
-        <v>0.41</v>
+        <v>0.34</v>
       </c>
       <c r="I13" s="14" t="inlineStr">
         <is>
@@ -1457,7 +1457,7 @@
         </is>
       </c>
       <c r="H14" s="11" t="n">
-        <v>0.19</v>
+        <v>0.06</v>
       </c>
       <c r="I14" s="11" t="inlineStr">
         <is>
@@ -1507,7 +1507,7 @@
         </is>
       </c>
       <c r="H15" s="14" t="n">
-        <v>0.25</v>
+        <v>0.32</v>
       </c>
       <c r="I15" s="14" t="inlineStr">
         <is>
@@ -1557,7 +1557,7 @@
         </is>
       </c>
       <c r="H16" s="11" t="n">
-        <v>0.19</v>
+        <v>0.3</v>
       </c>
       <c r="I16" s="11" t="inlineStr">
         <is>
@@ -1607,7 +1607,7 @@
         </is>
       </c>
       <c r="H17" s="14" t="n">
-        <v>0.2</v>
+        <v>0.16</v>
       </c>
       <c r="I17" s="14" t="inlineStr">
         <is>
@@ -1657,7 +1657,7 @@
         </is>
       </c>
       <c r="H18" s="11" t="n">
-        <v>0.23</v>
+        <v>0.35</v>
       </c>
       <c r="I18" s="11" t="inlineStr">
         <is>
@@ -1757,7 +1757,7 @@
         </is>
       </c>
       <c r="H20" s="11" t="n">
-        <v>0.39</v>
+        <v>0.32</v>
       </c>
       <c r="I20" s="11" t="inlineStr">
         <is>
@@ -1807,7 +1807,7 @@
         </is>
       </c>
       <c r="H21" s="14" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="I21" s="14" t="inlineStr">
         <is>
@@ -1857,7 +1857,7 @@
         </is>
       </c>
       <c r="H22" s="11" t="n">
-        <v>0.06</v>
+        <v>0.31</v>
       </c>
       <c r="I22" s="11" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         </is>
       </c>
       <c r="H23" s="14" t="n">
-        <v>0.09</v>
+        <v>0.15</v>
       </c>
       <c r="I23" s="14" t="inlineStr">
         <is>
@@ -1957,7 +1957,7 @@
         </is>
       </c>
       <c r="H24" s="11" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.24</v>
       </c>
       <c r="I24" s="11" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
         </is>
       </c>
       <c r="H25" s="14" t="n">
-        <v>0.26</v>
+        <v>0.41</v>
       </c>
       <c r="I25" s="14" t="inlineStr">
         <is>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="H26" s="11" t="n">
-        <v>0.34</v>
+        <v>0.16</v>
       </c>
       <c r="I26" s="11" t="inlineStr">
         <is>
@@ -2107,7 +2107,7 @@
         </is>
       </c>
       <c r="H27" s="14" t="n">
-        <v>0.29</v>
+        <v>0.21</v>
       </c>
       <c r="I27" s="14" t="inlineStr">
         <is>
@@ -2157,7 +2157,7 @@
         </is>
       </c>
       <c r="H28" s="11" t="n">
-        <v>0.14</v>
+        <v>0.05</v>
       </c>
       <c r="I28" s="11" t="inlineStr">
         <is>
@@ -2257,7 +2257,7 @@
         </is>
       </c>
       <c r="H30" s="11" t="n">
-        <v>0.29</v>
+        <v>0.24</v>
       </c>
       <c r="I30" s="11" t="inlineStr">
         <is>
@@ -2307,7 +2307,7 @@
         </is>
       </c>
       <c r="H31" s="14" t="n">
-        <v>0.39</v>
+        <v>0.08</v>
       </c>
       <c r="I31" s="14" t="inlineStr">
         <is>
@@ -2407,7 +2407,7 @@
         </is>
       </c>
       <c r="H33" s="14" t="n">
-        <v>0.1</v>
+        <v>0.19</v>
       </c>
       <c r="I33" s="14" t="inlineStr">
         <is>
@@ -2457,7 +2457,7 @@
         </is>
       </c>
       <c r="H34" s="11" t="n">
-        <v>0.22</v>
+        <v>0.08</v>
       </c>
       <c r="I34" s="11" t="inlineStr">
         <is>
@@ -2507,7 +2507,7 @@
         </is>
       </c>
       <c r="H35" s="14" t="n">
-        <v>0.08</v>
+        <v>0.16</v>
       </c>
       <c r="I35" s="14" t="inlineStr">
         <is>
@@ -2607,7 +2607,7 @@
         </is>
       </c>
       <c r="H37" s="14" t="n">
-        <v>0.2</v>
+        <v>0.13</v>
       </c>
       <c r="I37" s="14" t="inlineStr">
         <is>
@@ -2657,7 +2657,7 @@
         </is>
       </c>
       <c r="H38" s="11" t="n">
-        <v>0.14</v>
+        <v>0.27</v>
       </c>
       <c r="I38" s="11" t="inlineStr">
         <is>
@@ -2707,7 +2707,7 @@
         </is>
       </c>
       <c r="H39" s="14" t="n">
-        <v>0.25</v>
+        <v>0.42</v>
       </c>
       <c r="I39" s="14" t="inlineStr">
         <is>
@@ -2757,7 +2757,7 @@
         </is>
       </c>
       <c r="H40" s="11" t="n">
-        <v>0.2</v>
+        <v>0.29</v>
       </c>
       <c r="I40" s="11" t="inlineStr">
         <is>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="H41" s="14" t="n">
-        <v>0.21</v>
+        <v>0.25</v>
       </c>
       <c r="I41" s="14" t="inlineStr">
         <is>
@@ -2857,7 +2857,7 @@
         </is>
       </c>
       <c r="H42" s="11" t="n">
-        <v>0.1</v>
+        <v>0.14</v>
       </c>
       <c r="I42" s="11" t="inlineStr">
         <is>
@@ -2907,7 +2907,7 @@
         </is>
       </c>
       <c r="H43" s="14" t="n">
-        <v>0.12</v>
+        <v>0.42</v>
       </c>
       <c r="I43" s="14" t="inlineStr">
         <is>
@@ -2957,7 +2957,7 @@
         </is>
       </c>
       <c r="H44" s="11" t="n">
-        <v>0.31</v>
+        <v>0.08</v>
       </c>
       <c r="I44" s="11" t="inlineStr">
         <is>
@@ -3007,7 +3007,7 @@
         </is>
       </c>
       <c r="H45" s="14" t="n">
-        <v>0.43</v>
+        <v>0.19</v>
       </c>
       <c r="I45" s="14" t="inlineStr">
         <is>
@@ -3057,7 +3057,7 @@
         </is>
       </c>
       <c r="H46" s="11" t="n">
-        <v>0.31</v>
+        <v>0.24</v>
       </c>
       <c r="I46" s="11" t="inlineStr">
         <is>
@@ -3107,7 +3107,7 @@
         </is>
       </c>
       <c r="H47" s="14" t="n">
-        <v>0.27</v>
+        <v>0.38</v>
       </c>
       <c r="I47" s="14" t="inlineStr">
         <is>
@@ -3157,7 +3157,7 @@
         </is>
       </c>
       <c r="H48" s="11" t="n">
-        <v>0.26</v>
+        <v>0.37</v>
       </c>
       <c r="I48" s="11" t="inlineStr">
         <is>
@@ -3207,7 +3207,7 @@
         </is>
       </c>
       <c r="H49" s="14" t="n">
-        <v>0.27</v>
+        <v>0.16</v>
       </c>
       <c r="I49" s="14" t="inlineStr">
         <is>
@@ -3257,7 +3257,7 @@
         </is>
       </c>
       <c r="H50" s="11" t="n">
-        <v>0.39</v>
+        <v>0.38</v>
       </c>
       <c r="I50" s="11" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
         </is>
       </c>
       <c r="H51" s="14" t="n">
-        <v>0.23</v>
+        <v>0.37</v>
       </c>
       <c r="I51" s="14" t="inlineStr">
         <is>
@@ -3357,7 +3357,7 @@
         </is>
       </c>
       <c r="H52" s="11" t="n">
-        <v>0.42</v>
+        <v>0.32</v>
       </c>
       <c r="I52" s="11" t="inlineStr">
         <is>
@@ -3407,7 +3407,7 @@
         </is>
       </c>
       <c r="H53" s="14" t="n">
-        <v>0.39</v>
+        <v>0.25</v>
       </c>
       <c r="I53" s="14" t="inlineStr">
         <is>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="H54" s="11" t="n">
-        <v>0.25</v>
+        <v>0.11</v>
       </c>
       <c r="I54" s="11" t="inlineStr">
         <is>
@@ -3507,7 +3507,7 @@
         </is>
       </c>
       <c r="H55" s="14" t="n">
-        <v>0.35</v>
+        <v>0.21</v>
       </c>
       <c r="I55" s="14" t="inlineStr">
         <is>
@@ -3557,7 +3557,7 @@
         </is>
       </c>
       <c r="H56" s="11" t="n">
-        <v>0.4</v>
+        <v>0.39</v>
       </c>
       <c r="I56" s="11" t="inlineStr">
         <is>
@@ -3607,7 +3607,7 @@
         </is>
       </c>
       <c r="H57" s="14" t="n">
-        <v>0.14</v>
+        <v>0.16</v>
       </c>
       <c r="I57" s="14" t="inlineStr">
         <is>
@@ -3657,7 +3657,7 @@
         </is>
       </c>
       <c r="H58" s="11" t="n">
-        <v>0.25</v>
+        <v>0.32</v>
       </c>
       <c r="I58" s="11" t="inlineStr">
         <is>
@@ -3707,7 +3707,7 @@
         </is>
       </c>
       <c r="H59" s="14" t="n">
-        <v>0.08</v>
+        <v>0.34</v>
       </c>
       <c r="I59" s="14" t="inlineStr">
         <is>
@@ -3757,7 +3757,7 @@
         </is>
       </c>
       <c r="H60" s="11" t="n">
-        <v>0.38</v>
+        <v>0.4</v>
       </c>
       <c r="I60" s="11" t="inlineStr">
         <is>
@@ -3807,7 +3807,7 @@
         </is>
       </c>
       <c r="H61" s="14" t="n">
-        <v>0.2</v>
+        <v>0.34</v>
       </c>
       <c r="I61" s="14" t="inlineStr">
         <is>
@@ -3857,7 +3857,7 @@
         </is>
       </c>
       <c r="H62" s="11" t="n">
-        <v>0.39</v>
+        <v>0.08</v>
       </c>
       <c r="I62" s="11" t="inlineStr">
         <is>
@@ -3907,7 +3907,7 @@
         </is>
       </c>
       <c r="H63" s="14" t="n">
-        <v>0.23</v>
+        <v>0.1</v>
       </c>
       <c r="I63" s="14" t="inlineStr">
         <is>
@@ -3957,7 +3957,7 @@
         </is>
       </c>
       <c r="H64" s="11" t="n">
-        <v>0.28</v>
+        <v>0.05</v>
       </c>
       <c r="I64" s="11" t="inlineStr">
         <is>
@@ -4007,7 +4007,7 @@
         </is>
       </c>
       <c r="H65" s="14" t="n">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="I65" s="14" t="inlineStr">
         <is>
@@ -4057,7 +4057,7 @@
         </is>
       </c>
       <c r="H66" s="11" t="n">
-        <v>0.24</v>
+        <v>0.18</v>
       </c>
       <c r="I66" s="11" t="inlineStr">
         <is>
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="H67" s="14" t="n">
-        <v>0.32</v>
+        <v>0.21</v>
       </c>
       <c r="I67" s="14" t="inlineStr">
         <is>
@@ -4157,7 +4157,7 @@
         </is>
       </c>
       <c r="H68" s="11" t="n">
-        <v>0.14</v>
+        <v>0.1</v>
       </c>
       <c r="I68" s="11" t="inlineStr">
         <is>
@@ -4207,7 +4207,7 @@
         </is>
       </c>
       <c r="H69" s="14" t="n">
-        <v>0.38</v>
+        <v>0.27</v>
       </c>
       <c r="I69" s="14" t="inlineStr">
         <is>
@@ -4257,7 +4257,7 @@
         </is>
       </c>
       <c r="H70" s="11" t="n">
-        <v>0.15</v>
+        <v>0.26</v>
       </c>
       <c r="I70" s="11" t="inlineStr">
         <is>
@@ -4307,7 +4307,7 @@
         </is>
       </c>
       <c r="H71" s="14" t="n">
-        <v>0.26</v>
+        <v>0.3</v>
       </c>
       <c r="I71" s="14" t="inlineStr">
         <is>
@@ -4357,7 +4357,7 @@
         </is>
       </c>
       <c r="H72" s="11" t="n">
-        <v>0.06</v>
+        <v>0.18</v>
       </c>
       <c r="I72" s="11" t="inlineStr">
         <is>
@@ -4407,7 +4407,7 @@
         </is>
       </c>
       <c r="H73" s="14" t="n">
-        <v>0.18</v>
+        <v>0.36</v>
       </c>
       <c r="I73" s="14" t="inlineStr">
         <is>
@@ -4457,7 +4457,7 @@
         </is>
       </c>
       <c r="H74" s="11" t="n">
-        <v>0.08</v>
+        <v>0.12</v>
       </c>
       <c r="I74" s="11" t="inlineStr">
         <is>
@@ -4507,7 +4507,7 @@
         </is>
       </c>
       <c r="H75" s="14" t="n">
-        <v>0.18</v>
+        <v>0.38</v>
       </c>
       <c r="I75" s="14" t="inlineStr">
         <is>
@@ -4557,7 +4557,7 @@
         </is>
       </c>
       <c r="H76" s="11" t="n">
-        <v>0.08</v>
+        <v>0.33</v>
       </c>
       <c r="I76" s="11" t="inlineStr">
         <is>
@@ -4607,7 +4607,7 @@
         </is>
       </c>
       <c r="H77" s="14" t="n">
-        <v>0.32</v>
+        <v>0.38</v>
       </c>
       <c r="I77" s="14" t="inlineStr">
         <is>
@@ -4657,7 +4657,7 @@
         </is>
       </c>
       <c r="H78" s="11" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="I78" s="11" t="inlineStr">
         <is>
@@ -4757,7 +4757,7 @@
         </is>
       </c>
       <c r="H80" s="11" t="n">
-        <v>0.37</v>
+        <v>0.05</v>
       </c>
       <c r="I80" s="11" t="inlineStr">
         <is>
@@ -4807,7 +4807,7 @@
         </is>
       </c>
       <c r="H81" s="14" t="n">
-        <v>0.06</v>
+        <v>0.28</v>
       </c>
       <c r="I81" s="14" t="inlineStr">
         <is>
@@ -4857,7 +4857,7 @@
         </is>
       </c>
       <c r="H82" s="11" t="n">
-        <v>0.41</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I82" s="11" t="inlineStr">
         <is>
@@ -4907,7 +4907,7 @@
         </is>
       </c>
       <c r="H83" s="14" t="n">
-        <v>0.15</v>
+        <v>0.43</v>
       </c>
       <c r="I83" s="14" t="inlineStr">
         <is>
@@ -4957,7 +4957,7 @@
         </is>
       </c>
       <c r="H84" s="11" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="I84" s="11" t="inlineStr">
         <is>
@@ -5007,7 +5007,7 @@
         </is>
       </c>
       <c r="H85" s="14" t="n">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="I85" s="14" t="inlineStr">
         <is>
@@ -5057,7 +5057,7 @@
         </is>
       </c>
       <c r="H86" s="11" t="n">
-        <v>0.15</v>
+        <v>0.39</v>
       </c>
       <c r="I86" s="11" t="inlineStr">
         <is>
@@ -5107,7 +5107,7 @@
         </is>
       </c>
       <c r="H87" s="14" t="n">
-        <v>0.06</v>
+        <v>0.23</v>
       </c>
       <c r="I87" s="14" t="inlineStr">
         <is>
@@ -5157,7 +5157,7 @@
         </is>
       </c>
       <c r="H88" s="11" t="n">
-        <v>0.2</v>
+        <v>0.38</v>
       </c>
       <c r="I88" s="11" t="inlineStr">
         <is>
@@ -5207,7 +5207,7 @@
         </is>
       </c>
       <c r="H89" s="14" t="n">
-        <v>0.05</v>
+        <v>0.17</v>
       </c>
       <c r="I89" s="14" t="inlineStr">
         <is>
@@ -5257,7 +5257,7 @@
         </is>
       </c>
       <c r="H90" s="11" t="n">
-        <v>0.11</v>
+        <v>0.27</v>
       </c>
       <c r="I90" s="11" t="inlineStr">
         <is>
@@ -5307,7 +5307,7 @@
         </is>
       </c>
       <c r="H91" s="14" t="n">
-        <v>0.41</v>
+        <v>0.22</v>
       </c>
       <c r="I91" s="14" t="inlineStr">
         <is>
@@ -5357,7 +5357,7 @@
         </is>
       </c>
       <c r="H92" s="11" t="n">
-        <v>0.12</v>
+        <v>0.42</v>
       </c>
       <c r="I92" s="11" t="inlineStr">
         <is>
@@ -5407,7 +5407,7 @@
         </is>
       </c>
       <c r="H93" s="14" t="n">
-        <v>0.17</v>
+        <v>0.2</v>
       </c>
       <c r="I93" s="14" t="inlineStr">
         <is>
@@ -5457,7 +5457,7 @@
         </is>
       </c>
       <c r="H94" s="11" t="n">
-        <v>0.18</v>
+        <v>0.38</v>
       </c>
       <c r="I94" s="11" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="H95" s="14" t="n">
-        <v>0.15</v>
+        <v>0.41</v>
       </c>
       <c r="I95" s="14" t="inlineStr">
         <is>
@@ -5557,7 +5557,7 @@
         </is>
       </c>
       <c r="H96" s="11" t="n">
-        <v>0.41</v>
+        <v>0.26</v>
       </c>
       <c r="I96" s="11" t="inlineStr">
         <is>
@@ -5607,7 +5607,7 @@
         </is>
       </c>
       <c r="H97" s="14" t="n">
-        <v>0.27</v>
+        <v>0.39</v>
       </c>
       <c r="I97" s="14" t="inlineStr">
         <is>
@@ -5657,7 +5657,7 @@
         </is>
       </c>
       <c r="H98" s="11" t="n">
-        <v>0.35</v>
+        <v>0.11</v>
       </c>
       <c r="I98" s="11" t="inlineStr">
         <is>
@@ -5707,7 +5707,7 @@
         </is>
       </c>
       <c r="H99" s="14" t="n">
-        <v>0.42</v>
+        <v>0.44</v>
       </c>
       <c r="I99" s="14" t="inlineStr">
         <is>
@@ -5757,7 +5757,7 @@
         </is>
       </c>
       <c r="H100" s="11" t="n">
-        <v>0.06</v>
+        <v>0.36</v>
       </c>
       <c r="I100" s="11" t="inlineStr">
         <is>
@@ -5807,7 +5807,7 @@
         </is>
       </c>
       <c r="H101" s="14" t="n">
-        <v>0.08</v>
+        <v>0.32</v>
       </c>
       <c r="I101" s="14" t="inlineStr">
         <is>
@@ -5857,7 +5857,7 @@
         </is>
       </c>
       <c r="H102" s="11" t="n">
-        <v>0.09</v>
+        <v>0.32</v>
       </c>
       <c r="I102" s="11" t="inlineStr">
         <is>
@@ -5907,7 +5907,7 @@
         </is>
       </c>
       <c r="H103" s="14" t="n">
-        <v>0.31</v>
+        <v>0.36</v>
       </c>
       <c r="I103" s="14" t="inlineStr">
         <is>
@@ -5957,7 +5957,7 @@
         </is>
       </c>
       <c r="H104" s="11" t="n">
-        <v>0.22</v>
+        <v>0.32</v>
       </c>
       <c r="I104" s="11" t="inlineStr">
         <is>
@@ -6007,7 +6007,7 @@
         </is>
       </c>
       <c r="H105" s="14" t="n">
-        <v>0.12</v>
+        <v>0.24</v>
       </c>
       <c r="I105" s="14" t="inlineStr">
         <is>
@@ -6057,7 +6057,7 @@
         </is>
       </c>
       <c r="H106" s="11" t="n">
-        <v>0.11</v>
+        <v>0.38</v>
       </c>
       <c r="I106" s="11" t="inlineStr">
         <is>
@@ -6107,7 +6107,7 @@
         </is>
       </c>
       <c r="H107" s="14" t="n">
-        <v>0.1</v>
+        <v>0.33</v>
       </c>
       <c r="I107" s="14" t="inlineStr">
         <is>
@@ -6157,7 +6157,7 @@
         </is>
       </c>
       <c r="H108" s="11" t="n">
-        <v>0.4</v>
+        <v>0.35</v>
       </c>
       <c r="I108" s="11" t="inlineStr">
         <is>
@@ -6207,7 +6207,7 @@
         </is>
       </c>
       <c r="H109" s="14" t="n">
-        <v>0.45</v>
+        <v>0.44</v>
       </c>
       <c r="I109" s="14" t="inlineStr">
         <is>
@@ -6257,7 +6257,7 @@
         </is>
       </c>
       <c r="H110" s="11" t="n">
-        <v>0.24</v>
+        <v>0.3</v>
       </c>
       <c r="I110" s="11" t="inlineStr">
         <is>
@@ -6307,7 +6307,7 @@
         </is>
       </c>
       <c r="H111" s="14" t="n">
-        <v>0.3</v>
+        <v>0.33</v>
       </c>
       <c r="I111" s="14" t="inlineStr">
         <is>
@@ -6357,7 +6357,7 @@
         </is>
       </c>
       <c r="H112" s="11" t="n">
-        <v>0.18</v>
+        <v>0.45</v>
       </c>
       <c r="I112" s="11" t="inlineStr">
         <is>
@@ -6407,7 +6407,7 @@
         </is>
       </c>
       <c r="H113" s="14" t="n">
-        <v>0.31</v>
+        <v>0.36</v>
       </c>
       <c r="I113" s="14" t="inlineStr">
         <is>
@@ -6457,7 +6457,7 @@
         </is>
       </c>
       <c r="H114" s="11" t="n">
-        <v>0.12</v>
+        <v>0.32</v>
       </c>
       <c r="I114" s="11" t="inlineStr">
         <is>
@@ -6507,7 +6507,7 @@
         </is>
       </c>
       <c r="H115" s="14" t="n">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="I115" s="14" t="inlineStr">
         <is>
@@ -6557,7 +6557,7 @@
         </is>
       </c>
       <c r="H116" s="11" t="n">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="I116" s="11" t="inlineStr">
         <is>
@@ -6607,7 +6607,7 @@
         </is>
       </c>
       <c r="H117" s="14" t="n">
-        <v>0.31</v>
+        <v>0.2</v>
       </c>
       <c r="I117" s="14" t="inlineStr">
         <is>
@@ -6657,7 +6657,7 @@
         </is>
       </c>
       <c r="H118" s="11" t="n">
-        <v>0.24</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I118" s="11" t="inlineStr">
         <is>
@@ -6707,7 +6707,7 @@
         </is>
       </c>
       <c r="H119" s="14" t="n">
-        <v>0.31</v>
+        <v>0.41</v>
       </c>
       <c r="I119" s="14" t="inlineStr">
         <is>
@@ -6757,7 +6757,7 @@
         </is>
       </c>
       <c r="H120" s="11" t="n">
-        <v>0.29</v>
+        <v>0.33</v>
       </c>
       <c r="I120" s="11" t="inlineStr">
         <is>
@@ -6807,7 +6807,7 @@
         </is>
       </c>
       <c r="H121" s="14" t="n">
-        <v>0.17</v>
+        <v>0.38</v>
       </c>
       <c r="I121" s="14" t="inlineStr">
         <is>
@@ -6857,7 +6857,7 @@
         </is>
       </c>
       <c r="H122" s="11" t="n">
-        <v>0.37</v>
+        <v>0.12</v>
       </c>
       <c r="I122" s="11" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="H123" s="14" t="n">
-        <v>0.22</v>
+        <v>0.09</v>
       </c>
       <c r="I123" s="14" t="inlineStr">
         <is>
@@ -6957,7 +6957,7 @@
         </is>
       </c>
       <c r="H124" s="11" t="n">
-        <v>0.43</v>
+        <v>0.4</v>
       </c>
       <c r="I124" s="11" t="inlineStr">
         <is>
@@ -7007,7 +7007,7 @@
         </is>
       </c>
       <c r="H125" s="14" t="n">
-        <v>0.44</v>
+        <v>0.14</v>
       </c>
       <c r="I125" s="14" t="inlineStr">
         <is>
@@ -7057,7 +7057,7 @@
         </is>
       </c>
       <c r="H126" s="11" t="n">
-        <v>0.4</v>
+        <v>0.24</v>
       </c>
       <c r="I126" s="11" t="inlineStr">
         <is>
@@ -7107,7 +7107,7 @@
         </is>
       </c>
       <c r="H127" s="14" t="n">
-        <v>0.43</v>
+        <v>0.13</v>
       </c>
       <c r="I127" s="14" t="inlineStr">
         <is>
@@ -7157,7 +7157,7 @@
         </is>
       </c>
       <c r="H128" s="11" t="n">
-        <v>0.32</v>
+        <v>0.43</v>
       </c>
       <c r="I128" s="11" t="inlineStr">
         <is>
@@ -7207,7 +7207,7 @@
         </is>
       </c>
       <c r="H129" s="14" t="n">
-        <v>0.37</v>
+        <v>0.31</v>
       </c>
       <c r="I129" s="14" t="inlineStr">
         <is>
@@ -7257,7 +7257,7 @@
         </is>
       </c>
       <c r="H130" s="11" t="n">
-        <v>0.21</v>
+        <v>0.14</v>
       </c>
       <c r="I130" s="11" t="inlineStr">
         <is>
@@ -7307,7 +7307,7 @@
         </is>
       </c>
       <c r="H131" s="14" t="n">
-        <v>0.43</v>
+        <v>0.25</v>
       </c>
       <c r="I131" s="14" t="inlineStr">
         <is>
@@ -7357,7 +7357,7 @@
         </is>
       </c>
       <c r="H132" s="11" t="n">
-        <v>0.23</v>
+        <v>0.12</v>
       </c>
       <c r="I132" s="11" t="inlineStr">
         <is>
@@ -7407,7 +7407,7 @@
         </is>
       </c>
       <c r="H133" s="14" t="n">
-        <v>0.12</v>
+        <v>0.21</v>
       </c>
       <c r="I133" s="14" t="inlineStr">
         <is>
@@ -7457,7 +7457,7 @@
         </is>
       </c>
       <c r="H134" s="11" t="n">
-        <v>0.1</v>
+        <v>0.23</v>
       </c>
       <c r="I134" s="11" t="inlineStr">
         <is>
@@ -7507,7 +7507,7 @@
         </is>
       </c>
       <c r="H135" s="14" t="n">
-        <v>0.06</v>
+        <v>0.23</v>
       </c>
       <c r="I135" s="14" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="H136" s="11" t="n">
-        <v>0.29</v>
+        <v>0.4</v>
       </c>
       <c r="I136" s="11" t="inlineStr">
         <is>
@@ -7607,7 +7607,7 @@
         </is>
       </c>
       <c r="H137" s="14" t="n">
-        <v>0.34</v>
+        <v>0.1</v>
       </c>
       <c r="I137" s="14" t="inlineStr">
         <is>
@@ -7657,7 +7657,7 @@
         </is>
       </c>
       <c r="H138" s="11" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.25</v>
       </c>
       <c r="I138" s="11" t="inlineStr">
         <is>
@@ -7707,7 +7707,7 @@
         </is>
       </c>
       <c r="H139" s="14" t="n">
-        <v>0.21</v>
+        <v>0.08</v>
       </c>
       <c r="I139" s="14" t="inlineStr">
         <is>
@@ -7757,7 +7757,7 @@
         </is>
       </c>
       <c r="H140" s="11" t="n">
-        <v>0.4</v>
+        <v>0.17</v>
       </c>
       <c r="I140" s="11" t="inlineStr">
         <is>
@@ -7807,7 +7807,7 @@
         </is>
       </c>
       <c r="H141" s="14" t="n">
-        <v>0.05</v>
+        <v>0.3</v>
       </c>
       <c r="I141" s="14" t="inlineStr">
         <is>
@@ -7857,7 +7857,7 @@
         </is>
       </c>
       <c r="H142" s="11" t="n">
-        <v>0.27</v>
+        <v>0.37</v>
       </c>
       <c r="I142" s="11" t="inlineStr">
         <is>
@@ -7907,7 +7907,7 @@
         </is>
       </c>
       <c r="H143" s="14" t="n">
-        <v>0.4</v>
+        <v>0.15</v>
       </c>
       <c r="I143" s="14" t="inlineStr">
         <is>
@@ -7957,7 +7957,7 @@
         </is>
       </c>
       <c r="H144" s="11" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="I144" s="11" t="inlineStr">
         <is>
@@ -8007,7 +8007,7 @@
         </is>
       </c>
       <c r="H145" s="14" t="n">
-        <v>0.32</v>
+        <v>0.27</v>
       </c>
       <c r="I145" s="14" t="inlineStr">
         <is>
@@ -8057,7 +8057,7 @@
         </is>
       </c>
       <c r="H146" s="11" t="n">
-        <v>0.16</v>
+        <v>0.24</v>
       </c>
       <c r="I146" s="11" t="inlineStr">
         <is>
@@ -8107,7 +8107,7 @@
         </is>
       </c>
       <c r="H147" s="14" t="n">
-        <v>0.11</v>
+        <v>0.17</v>
       </c>
       <c r="I147" s="14" t="inlineStr">
         <is>
@@ -8157,7 +8157,7 @@
         </is>
       </c>
       <c r="H148" s="11" t="n">
-        <v>0.27</v>
+        <v>0.44</v>
       </c>
       <c r="I148" s="11" t="inlineStr">
         <is>
@@ -8207,7 +8207,7 @@
         </is>
       </c>
       <c r="H149" s="14" t="n">
-        <v>0.36</v>
+        <v>0.2</v>
       </c>
       <c r="I149" s="14" t="inlineStr">
         <is>
@@ -8257,7 +8257,7 @@
         </is>
       </c>
       <c r="H150" s="11" t="n">
-        <v>0.3</v>
+        <v>0.28</v>
       </c>
       <c r="I150" s="11" t="inlineStr">
         <is>
@@ -8307,7 +8307,7 @@
         </is>
       </c>
       <c r="H151" s="14" t="n">
-        <v>0.38</v>
+        <v>0.14</v>
       </c>
       <c r="I151" s="14" t="inlineStr">
         <is>
@@ -8357,7 +8357,7 @@
         </is>
       </c>
       <c r="H152" s="11" t="n">
-        <v>0.08</v>
+        <v>0.24</v>
       </c>
       <c r="I152" s="11" t="inlineStr">
         <is>
@@ -8457,7 +8457,7 @@
         </is>
       </c>
       <c r="H154" s="11" t="n">
-        <v>0.3</v>
+        <v>0.06</v>
       </c>
       <c r="I154" s="11" t="inlineStr">
         <is>
@@ -8507,7 +8507,7 @@
         </is>
       </c>
       <c r="H155" s="14" t="n">
-        <v>0.08</v>
+        <v>0.33</v>
       </c>
       <c r="I155" s="14" t="inlineStr">
         <is>
@@ -8557,7 +8557,7 @@
         </is>
       </c>
       <c r="H156" s="11" t="n">
-        <v>0.14</v>
+        <v>0.23</v>
       </c>
       <c r="I156" s="11" t="inlineStr">
         <is>
@@ -8607,7 +8607,7 @@
         </is>
       </c>
       <c r="H157" s="14" t="n">
-        <v>0.06</v>
+        <v>0.14</v>
       </c>
       <c r="I157" s="14" t="inlineStr">
         <is>
@@ -8657,7 +8657,7 @@
         </is>
       </c>
       <c r="H158" s="11" t="n">
-        <v>0.3</v>
+        <v>0.25</v>
       </c>
       <c r="I158" s="11" t="inlineStr">
         <is>
@@ -8707,7 +8707,7 @@
         </is>
       </c>
       <c r="H159" s="14" t="n">
-        <v>0.29</v>
+        <v>0.4</v>
       </c>
       <c r="I159" s="14" t="inlineStr">
         <is>
@@ -8757,7 +8757,7 @@
         </is>
       </c>
       <c r="H160" s="11" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.33</v>
       </c>
       <c r="I160" s="11" t="inlineStr">
         <is>
@@ -8807,7 +8807,7 @@
         </is>
       </c>
       <c r="H161" s="14" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="I161" s="14" t="inlineStr">
         <is>
@@ -8857,7 +8857,7 @@
         </is>
       </c>
       <c r="H162" s="11" t="n">
-        <v>0.38</v>
+        <v>0.37</v>
       </c>
       <c r="I162" s="11" t="inlineStr">
         <is>
@@ -8907,7 +8907,7 @@
         </is>
       </c>
       <c r="H163" s="14" t="n">
-        <v>0.44</v>
+        <v>0.21</v>
       </c>
       <c r="I163" s="14" t="inlineStr">
         <is>
@@ -8957,7 +8957,7 @@
         </is>
       </c>
       <c r="H164" s="11" t="n">
-        <v>0.24</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I164" s="11" t="inlineStr">
         <is>
@@ -9007,7 +9007,7 @@
         </is>
       </c>
       <c r="H165" s="14" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="I165" s="14" t="inlineStr">
         <is>
@@ -9057,7 +9057,7 @@
         </is>
       </c>
       <c r="H166" s="11" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.21</v>
       </c>
       <c r="I166" s="11" t="inlineStr">
         <is>
@@ -9107,7 +9107,7 @@
         </is>
       </c>
       <c r="H167" s="14" t="n">
-        <v>0.43</v>
+        <v>0.37</v>
       </c>
       <c r="I167" s="14" t="inlineStr">
         <is>
@@ -9157,7 +9157,7 @@
         </is>
       </c>
       <c r="H168" s="11" t="n">
-        <v>0.11</v>
+        <v>0.29</v>
       </c>
       <c r="I168" s="11" t="inlineStr">
         <is>
@@ -9207,7 +9207,7 @@
         </is>
       </c>
       <c r="H169" s="14" t="n">
-        <v>0.22</v>
+        <v>0.29</v>
       </c>
       <c r="I169" s="14" t="inlineStr">
         <is>
@@ -9307,7 +9307,7 @@
         </is>
       </c>
       <c r="H171" s="14" t="n">
-        <v>0.2</v>
+        <v>0.08</v>
       </c>
       <c r="I171" s="14" t="inlineStr">
         <is>
@@ -9357,7 +9357,7 @@
         </is>
       </c>
       <c r="H172" s="11" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="I172" s="11" t="inlineStr">
         <is>
@@ -9407,7 +9407,7 @@
         </is>
       </c>
       <c r="H173" s="14" t="n">
-        <v>0.15</v>
+        <v>0.4</v>
       </c>
       <c r="I173" s="14" t="inlineStr">
         <is>
@@ -9457,7 +9457,7 @@
         </is>
       </c>
       <c r="H174" s="11" t="n">
-        <v>0.41</v>
+        <v>0.19</v>
       </c>
       <c r="I174" s="11" t="inlineStr">
         <is>
@@ -9507,7 +9507,7 @@
         </is>
       </c>
       <c r="H175" s="14" t="n">
-        <v>0.37</v>
+        <v>0.33</v>
       </c>
       <c r="I175" s="14" t="inlineStr">
         <is>
@@ -9557,7 +9557,7 @@
         </is>
       </c>
       <c r="H176" s="11" t="n">
-        <v>0.23</v>
+        <v>0.37</v>
       </c>
       <c r="I176" s="11" t="inlineStr">
         <is>
@@ -9607,7 +9607,7 @@
         </is>
       </c>
       <c r="H177" s="14" t="n">
-        <v>0.28</v>
+        <v>0.24</v>
       </c>
       <c r="I177" s="14" t="inlineStr">
         <is>
@@ -9657,7 +9657,7 @@
         </is>
       </c>
       <c r="H178" s="11" t="n">
-        <v>0.12</v>
+        <v>0.43</v>
       </c>
       <c r="I178" s="11" t="inlineStr">
         <is>
@@ -9707,7 +9707,7 @@
         </is>
       </c>
       <c r="H179" s="14" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="I179" s="14" t="inlineStr">
         <is>
@@ -9757,7 +9757,7 @@
         </is>
       </c>
       <c r="H180" s="11" t="n">
-        <v>0.05</v>
+        <v>0.19</v>
       </c>
       <c r="I180" s="11" t="inlineStr">
         <is>
@@ -9807,7 +9807,7 @@
         </is>
       </c>
       <c r="H181" s="14" t="n">
-        <v>0.22</v>
+        <v>0.18</v>
       </c>
       <c r="I181" s="14" t="inlineStr">
         <is>
@@ -9857,7 +9857,7 @@
         </is>
       </c>
       <c r="H182" s="11" t="n">
-        <v>0.21</v>
+        <v>0.26</v>
       </c>
       <c r="I182" s="11" t="inlineStr">
         <is>
@@ -9907,7 +9907,7 @@
         </is>
       </c>
       <c r="H183" s="14" t="n">
-        <v>0.36</v>
+        <v>0.13</v>
       </c>
       <c r="I183" s="14" t="inlineStr">
         <is>
@@ -9957,7 +9957,7 @@
         </is>
       </c>
       <c r="H184" s="11" t="n">
-        <v>0.06</v>
+        <v>0.22</v>
       </c>
       <c r="I184" s="11" t="inlineStr">
         <is>
@@ -10007,7 +10007,7 @@
         </is>
       </c>
       <c r="H185" s="14" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="I185" s="14" t="inlineStr">
         <is>
@@ -10057,7 +10057,7 @@
         </is>
       </c>
       <c r="H186" s="11" t="n">
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="I186" s="11" t="inlineStr">
         <is>
@@ -10107,7 +10107,7 @@
         </is>
       </c>
       <c r="H187" s="14" t="n">
-        <v>0.32</v>
+        <v>0.14</v>
       </c>
       <c r="I187" s="14" t="inlineStr">
         <is>
@@ -10157,7 +10157,7 @@
         </is>
       </c>
       <c r="H188" s="11" t="n">
-        <v>0.32</v>
+        <v>0.29</v>
       </c>
       <c r="I188" s="11" t="inlineStr">
         <is>
@@ -10207,7 +10207,7 @@
         </is>
       </c>
       <c r="H189" s="14" t="n">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="I189" s="14" t="inlineStr">
         <is>
@@ -10307,7 +10307,7 @@
         </is>
       </c>
       <c r="H191" s="14" t="n">
-        <v>0.28</v>
+        <v>0.2</v>
       </c>
       <c r="I191" s="14" t="inlineStr">
         <is>
@@ -10357,7 +10357,7 @@
         </is>
       </c>
       <c r="H192" s="11" t="n">
-        <v>0.29</v>
+        <v>0.12</v>
       </c>
       <c r="I192" s="11" t="inlineStr">
         <is>
@@ -10407,7 +10407,7 @@
         </is>
       </c>
       <c r="H193" s="14" t="n">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
       <c r="I193" s="14" t="inlineStr">
         <is>
@@ -10457,7 +10457,7 @@
         </is>
       </c>
       <c r="H194" s="11" t="n">
-        <v>0.14</v>
+        <v>0.36</v>
       </c>
       <c r="I194" s="11" t="inlineStr">
         <is>
@@ -10507,7 +10507,7 @@
         </is>
       </c>
       <c r="H195" s="14" t="n">
-        <v>0.31</v>
+        <v>0.14</v>
       </c>
       <c r="I195" s="14" t="inlineStr">
         <is>
@@ -10557,7 +10557,7 @@
         </is>
       </c>
       <c r="H196" s="11" t="n">
-        <v>0.23</v>
+        <v>0.32</v>
       </c>
       <c r="I196" s="11" t="inlineStr">
         <is>
@@ -10607,7 +10607,7 @@
         </is>
       </c>
       <c r="H197" s="14" t="n">
-        <v>0.13</v>
+        <v>0.21</v>
       </c>
       <c r="I197" s="14" t="inlineStr">
         <is>
@@ -10657,7 +10657,7 @@
         </is>
       </c>
       <c r="H198" s="11" t="n">
-        <v>0.18</v>
+        <v>0.3</v>
       </c>
       <c r="I198" s="11" t="inlineStr">
         <is>
@@ -10707,7 +10707,7 @@
         </is>
       </c>
       <c r="H199" s="14" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.17</v>
       </c>
       <c r="I199" s="14" t="inlineStr">
         <is>
@@ -10757,7 +10757,7 @@
         </is>
       </c>
       <c r="H200" s="11" t="n">
-        <v>0.16</v>
+        <v>0.39</v>
       </c>
       <c r="I200" s="11" t="inlineStr">
         <is>
@@ -10807,7 +10807,7 @@
         </is>
       </c>
       <c r="H201" s="14" t="n">
-        <v>0.06</v>
+        <v>0.18</v>
       </c>
       <c r="I201" s="14" t="inlineStr">
         <is>
@@ -10857,7 +10857,7 @@
         </is>
       </c>
       <c r="H202" s="11" t="n">
-        <v>0.22</v>
+        <v>0.39</v>
       </c>
       <c r="I202" s="11" t="inlineStr">
         <is>
@@ -10907,7 +10907,7 @@
         </is>
       </c>
       <c r="H203" s="14" t="n">
-        <v>0.37</v>
+        <v>0.23</v>
       </c>
       <c r="I203" s="14" t="inlineStr">
         <is>
@@ -10957,7 +10957,7 @@
         </is>
       </c>
       <c r="H204" s="11" t="n">
-        <v>0.26</v>
+        <v>0.17</v>
       </c>
       <c r="I204" s="11" t="inlineStr">
         <is>
@@ -11007,7 +11007,7 @@
         </is>
       </c>
       <c r="H205" s="14" t="n">
-        <v>0.34</v>
+        <v>0.06</v>
       </c>
       <c r="I205" s="14" t="inlineStr">
         <is>
@@ -11057,7 +11057,7 @@
         </is>
       </c>
       <c r="H206" s="11" t="n">
-        <v>0.27</v>
+        <v>0.23</v>
       </c>
       <c r="I206" s="11" t="inlineStr">
         <is>
@@ -11107,7 +11107,7 @@
         </is>
       </c>
       <c r="H207" s="14" t="n">
-        <v>0.35</v>
+        <v>0.27</v>
       </c>
       <c r="I207" s="14" t="inlineStr">
         <is>
@@ -11157,7 +11157,7 @@
         </is>
       </c>
       <c r="H208" s="11" t="n">
-        <v>0.31</v>
+        <v>0.2</v>
       </c>
       <c r="I208" s="11" t="inlineStr">
         <is>
@@ -11207,7 +11207,7 @@
         </is>
       </c>
       <c r="H209" s="14" t="n">
-        <v>0.18</v>
+        <v>0.41</v>
       </c>
       <c r="I209" s="14" t="inlineStr">
         <is>
@@ -11257,7 +11257,7 @@
         </is>
       </c>
       <c r="H210" s="11" t="n">
-        <v>0.35</v>
+        <v>0.16</v>
       </c>
       <c r="I210" s="11" t="inlineStr">
         <is>
@@ -11307,7 +11307,7 @@
         </is>
       </c>
       <c r="H211" s="14" t="n">
-        <v>0.42</v>
+        <v>0.16</v>
       </c>
       <c r="I211" s="14" t="inlineStr">
         <is>
@@ -11357,7 +11357,7 @@
         </is>
       </c>
       <c r="H212" s="11" t="n">
-        <v>0.34</v>
+        <v>0.26</v>
       </c>
       <c r="I212" s="11" t="inlineStr">
         <is>
@@ -11407,7 +11407,7 @@
         </is>
       </c>
       <c r="H213" s="14" t="n">
-        <v>0.41</v>
+        <v>0.4</v>
       </c>
       <c r="I213" s="14" t="inlineStr">
         <is>
@@ -11457,7 +11457,7 @@
         </is>
       </c>
       <c r="H214" s="11" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="I214" s="11" t="inlineStr">
         <is>
@@ -11557,7 +11557,7 @@
         </is>
       </c>
       <c r="H216" s="11" t="n">
-        <v>0.17</v>
+        <v>0.43</v>
       </c>
       <c r="I216" s="11" t="inlineStr">
         <is>
@@ -11607,7 +11607,7 @@
         </is>
       </c>
       <c r="H217" s="14" t="n">
-        <v>0.4</v>
+        <v>0.17</v>
       </c>
       <c r="I217" s="14" t="inlineStr">
         <is>
@@ -11657,7 +11657,7 @@
         </is>
       </c>
       <c r="H218" s="11" t="n">
-        <v>0.43</v>
+        <v>0.18</v>
       </c>
       <c r="I218" s="11" t="inlineStr">
         <is>
@@ -11707,7 +11707,7 @@
         </is>
       </c>
       <c r="H219" s="14" t="n">
-        <v>0.35</v>
+        <v>0.37</v>
       </c>
       <c r="I219" s="14" t="inlineStr">
         <is>
@@ -11757,7 +11757,7 @@
         </is>
       </c>
       <c r="H220" s="11" t="n">
-        <v>0.12</v>
+        <v>0.06</v>
       </c>
       <c r="I220" s="11" t="inlineStr">
         <is>
@@ -11807,7 +11807,7 @@
         </is>
       </c>
       <c r="H221" s="14" t="n">
-        <v>0.24</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I221" s="14" t="inlineStr">
         <is>
@@ -11857,7 +11857,7 @@
         </is>
       </c>
       <c r="H222" s="11" t="n">
-        <v>0.19</v>
+        <v>0.15</v>
       </c>
       <c r="I222" s="11" t="inlineStr">
         <is>
@@ -11907,7 +11907,7 @@
         </is>
       </c>
       <c r="H223" s="14" t="n">
-        <v>0.25</v>
+        <v>0.11</v>
       </c>
       <c r="I223" s="14" t="inlineStr">
         <is>
@@ -11957,7 +11957,7 @@
         </is>
       </c>
       <c r="H224" s="11" t="n">
-        <v>0.38</v>
+        <v>0.31</v>
       </c>
       <c r="I224" s="11" t="inlineStr">
         <is>
@@ -12007,7 +12007,7 @@
         </is>
       </c>
       <c r="H225" s="14" t="n">
-        <v>0.39</v>
+        <v>0.19</v>
       </c>
       <c r="I225" s="14" t="inlineStr">
         <is>
@@ -12057,7 +12057,7 @@
         </is>
       </c>
       <c r="H226" s="11" t="n">
-        <v>0.25</v>
+        <v>0.17</v>
       </c>
       <c r="I226" s="11" t="inlineStr">
         <is>
@@ -12107,7 +12107,7 @@
         </is>
       </c>
       <c r="H227" s="14" t="n">
-        <v>0.34</v>
+        <v>0.16</v>
       </c>
       <c r="I227" s="14" t="inlineStr">
         <is>
@@ -12157,7 +12157,7 @@
         </is>
       </c>
       <c r="H228" s="11" t="n">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="I228" s="11" t="inlineStr">
         <is>
@@ -12207,7 +12207,7 @@
         </is>
       </c>
       <c r="H229" s="14" t="n">
-        <v>0.18</v>
+        <v>0.13</v>
       </c>
       <c r="I229" s="14" t="inlineStr">
         <is>
@@ -12257,7 +12257,7 @@
         </is>
       </c>
       <c r="H230" s="11" t="n">
-        <v>0.18</v>
+        <v>0.12</v>
       </c>
       <c r="I230" s="11" t="inlineStr">
         <is>
@@ -12307,7 +12307,7 @@
         </is>
       </c>
       <c r="H231" s="14" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="I231" s="14" t="inlineStr">
         <is>
@@ -12357,7 +12357,7 @@
         </is>
       </c>
       <c r="H232" s="11" t="n">
-        <v>0.35</v>
+        <v>0.29</v>
       </c>
       <c r="I232" s="11" t="inlineStr">
         <is>
@@ -12407,7 +12407,7 @@
         </is>
       </c>
       <c r="H233" s="14" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="I233" s="14" t="inlineStr">
         <is>
@@ -12457,7 +12457,7 @@
         </is>
       </c>
       <c r="H234" s="11" t="n">
-        <v>0.36</v>
+        <v>0.11</v>
       </c>
       <c r="I234" s="11" t="inlineStr">
         <is>
@@ -12507,7 +12507,7 @@
         </is>
       </c>
       <c r="H235" s="14" t="n">
-        <v>0.37</v>
+        <v>0.13</v>
       </c>
       <c r="I235" s="14" t="inlineStr">
         <is>
@@ -12557,7 +12557,7 @@
         </is>
       </c>
       <c r="H236" s="11" t="n">
-        <v>0.22</v>
+        <v>0.19</v>
       </c>
       <c r="I236" s="11" t="inlineStr">
         <is>
@@ -12607,7 +12607,7 @@
         </is>
       </c>
       <c r="H237" s="14" t="n">
-        <v>0.45</v>
+        <v>0.29</v>
       </c>
       <c r="I237" s="14" t="inlineStr">
         <is>
@@ -12657,7 +12657,7 @@
         </is>
       </c>
       <c r="H238" s="11" t="n">
-        <v>0.44</v>
+        <v>0.28</v>
       </c>
       <c r="I238" s="11" t="inlineStr">
         <is>
@@ -12707,7 +12707,7 @@
         </is>
       </c>
       <c r="H239" s="14" t="n">
-        <v>0.09</v>
+        <v>0.29</v>
       </c>
       <c r="I239" s="14" t="inlineStr">
         <is>
@@ -12757,7 +12757,7 @@
         </is>
       </c>
       <c r="H240" s="11" t="n">
-        <v>0.27</v>
+        <v>0.44</v>
       </c>
       <c r="I240" s="11" t="inlineStr">
         <is>
@@ -12807,7 +12807,7 @@
         </is>
       </c>
       <c r="H241" s="14" t="n">
-        <v>0.08</v>
+        <v>0.24</v>
       </c>
       <c r="I241" s="14" t="inlineStr">
         <is>
@@ -12857,7 +12857,7 @@
         </is>
       </c>
       <c r="H242" s="11" t="n">
-        <v>0.33</v>
+        <v>0.06</v>
       </c>
       <c r="I242" s="11" t="inlineStr">
         <is>
@@ -12907,7 +12907,7 @@
         </is>
       </c>
       <c r="H243" s="14" t="n">
-        <v>0.2</v>
+        <v>0.11</v>
       </c>
       <c r="I243" s="14" t="inlineStr">
         <is>
@@ -12957,7 +12957,7 @@
         </is>
       </c>
       <c r="H244" s="11" t="n">
-        <v>0.26</v>
+        <v>0.13</v>
       </c>
       <c r="I244" s="11" t="inlineStr">
         <is>
@@ -13007,7 +13007,7 @@
         </is>
       </c>
       <c r="H245" s="14" t="n">
-        <v>0.39</v>
+        <v>0.41</v>
       </c>
       <c r="I245" s="14" t="inlineStr">
         <is>
@@ -13057,7 +13057,7 @@
         </is>
       </c>
       <c r="H246" s="11" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="I246" s="11" t="inlineStr">
         <is>
@@ -13107,7 +13107,7 @@
         </is>
       </c>
       <c r="H247" s="14" t="n">
-        <v>0.29</v>
+        <v>0.35</v>
       </c>
       <c r="I247" s="14" t="inlineStr">
         <is>
@@ -13157,7 +13157,7 @@
         </is>
       </c>
       <c r="H248" s="11" t="n">
-        <v>0.42</v>
+        <v>0.3</v>
       </c>
       <c r="I248" s="11" t="inlineStr">
         <is>
@@ -13207,7 +13207,7 @@
         </is>
       </c>
       <c r="H249" s="14" t="n">
-        <v>0.27</v>
+        <v>0.38</v>
       </c>
       <c r="I249" s="14" t="inlineStr">
         <is>
@@ -13257,7 +13257,7 @@
         </is>
       </c>
       <c r="H250" s="11" t="n">
-        <v>0.44</v>
+        <v>0.13</v>
       </c>
       <c r="I250" s="11" t="inlineStr">
         <is>
@@ -13307,7 +13307,7 @@
         </is>
       </c>
       <c r="H251" s="14" t="n">
-        <v>0.17</v>
+        <v>0.4</v>
       </c>
       <c r="I251" s="14" t="inlineStr">
         <is>
@@ -13357,7 +13357,7 @@
         </is>
       </c>
       <c r="H252" s="11" t="n">
-        <v>0.13</v>
+        <v>0.4</v>
       </c>
       <c r="I252" s="11" t="inlineStr">
         <is>
@@ -13407,7 +13407,7 @@
         </is>
       </c>
       <c r="H253" s="14" t="n">
-        <v>0.08</v>
+        <v>0.38</v>
       </c>
       <c r="I253" s="14" t="inlineStr">
         <is>
@@ -13457,7 +13457,7 @@
         </is>
       </c>
       <c r="H254" s="11" t="n">
-        <v>0.18</v>
+        <v>0.22</v>
       </c>
       <c r="I254" s="11" t="inlineStr">
         <is>
@@ -13507,7 +13507,7 @@
         </is>
       </c>
       <c r="H255" s="14" t="n">
-        <v>0.08</v>
+        <v>0.1</v>
       </c>
       <c r="I255" s="14" t="inlineStr">
         <is>
@@ -13557,7 +13557,7 @@
         </is>
       </c>
       <c r="H256" s="11" t="n">
-        <v>0.12</v>
+        <v>0.15</v>
       </c>
       <c r="I256" s="11" t="inlineStr">
         <is>
@@ -13607,7 +13607,7 @@
         </is>
       </c>
       <c r="H257" s="14" t="n">
-        <v>0.42</v>
+        <v>0.33</v>
       </c>
       <c r="I257" s="14" t="inlineStr">
         <is>
@@ -13657,7 +13657,7 @@
         </is>
       </c>
       <c r="H258" s="11" t="n">
-        <v>0.19</v>
+        <v>0.38</v>
       </c>
       <c r="I258" s="11" t="inlineStr">
         <is>
@@ -13707,7 +13707,7 @@
         </is>
       </c>
       <c r="H259" s="14" t="n">
-        <v>0.12</v>
+        <v>0.34</v>
       </c>
       <c r="I259" s="14" t="inlineStr">
         <is>
@@ -13757,7 +13757,7 @@
         </is>
       </c>
       <c r="H260" s="11" t="n">
-        <v>0.25</v>
+        <v>0.43</v>
       </c>
       <c r="I260" s="11" t="inlineStr">
         <is>
@@ -13807,7 +13807,7 @@
         </is>
       </c>
       <c r="H261" s="14" t="n">
-        <v>0.33</v>
+        <v>0.2</v>
       </c>
       <c r="I261" s="14" t="inlineStr">
         <is>
@@ -13857,7 +13857,7 @@
         </is>
       </c>
       <c r="H262" s="11" t="n">
-        <v>0.25</v>
+        <v>0.13</v>
       </c>
       <c r="I262" s="11" t="inlineStr">
         <is>
@@ -13907,7 +13907,7 @@
         </is>
       </c>
       <c r="H263" s="14" t="n">
-        <v>0.16</v>
+        <v>0.26</v>
       </c>
       <c r="I263" s="14" t="inlineStr">
         <is>
@@ -13957,7 +13957,7 @@
         </is>
       </c>
       <c r="H264" s="11" t="n">
-        <v>0.08</v>
+        <v>0.32</v>
       </c>
       <c r="I264" s="11" t="inlineStr">
         <is>
@@ -14007,7 +14007,7 @@
         </is>
       </c>
       <c r="H265" s="14" t="n">
-        <v>0.18</v>
+        <v>0.41</v>
       </c>
       <c r="I265" s="14" t="inlineStr">
         <is>
@@ -14057,7 +14057,7 @@
         </is>
       </c>
       <c r="H266" s="11" t="n">
-        <v>0.2</v>
+        <v>0.26</v>
       </c>
       <c r="I266" s="11" t="inlineStr">
         <is>
@@ -14107,7 +14107,7 @@
         </is>
       </c>
       <c r="H267" s="14" t="n">
-        <v>0.09</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I267" s="14" t="inlineStr">
         <is>
@@ -14157,7 +14157,7 @@
         </is>
       </c>
       <c r="H268" s="11" t="n">
-        <v>0.26</v>
+        <v>0.12</v>
       </c>
       <c r="I268" s="11" t="inlineStr">
         <is>
@@ -14207,7 +14207,7 @@
         </is>
       </c>
       <c r="H269" s="14" t="n">
-        <v>0.29</v>
+        <v>0.44</v>
       </c>
       <c r="I269" s="14" t="inlineStr">
         <is>
@@ -14257,7 +14257,7 @@
         </is>
       </c>
       <c r="H270" s="11" t="n">
-        <v>0.16</v>
+        <v>0.41</v>
       </c>
       <c r="I270" s="11" t="inlineStr">
         <is>
@@ -14307,7 +14307,7 @@
         </is>
       </c>
       <c r="H271" s="14" t="n">
-        <v>0.44</v>
+        <v>0.35</v>
       </c>
       <c r="I271" s="14" t="inlineStr">
         <is>
@@ -14357,7 +14357,7 @@
         </is>
       </c>
       <c r="H272" s="11" t="n">
-        <v>0.12</v>
+        <v>0.26</v>
       </c>
       <c r="I272" s="11" t="inlineStr">
         <is>
@@ -14407,7 +14407,7 @@
         </is>
       </c>
       <c r="H273" s="14" t="n">
-        <v>0.16</v>
+        <v>0.31</v>
       </c>
       <c r="I273" s="14" t="inlineStr">
         <is>
@@ -14457,7 +14457,7 @@
         </is>
       </c>
       <c r="H274" s="11" t="n">
-        <v>0.17</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I274" s="11" t="inlineStr">
         <is>
@@ -14507,7 +14507,7 @@
         </is>
       </c>
       <c r="H275" s="14" t="n">
-        <v>0.21</v>
+        <v>0.43</v>
       </c>
       <c r="I275" s="14" t="inlineStr">
         <is>
@@ -14557,7 +14557,7 @@
         </is>
       </c>
       <c r="H276" s="11" t="n">
-        <v>0.34</v>
+        <v>0.09</v>
       </c>
       <c r="I276" s="11" t="inlineStr">
         <is>
@@ -14607,7 +14607,7 @@
         </is>
       </c>
       <c r="H277" s="14" t="n">
-        <v>0.25</v>
+        <v>0.27</v>
       </c>
       <c r="I277" s="14" t="inlineStr">
         <is>
@@ -14657,7 +14657,7 @@
         </is>
       </c>
       <c r="H278" s="11" t="n">
-        <v>0.36</v>
+        <v>0.28</v>
       </c>
       <c r="I278" s="11" t="inlineStr">
         <is>
@@ -14707,7 +14707,7 @@
         </is>
       </c>
       <c r="H279" s="14" t="n">
-        <v>0.4</v>
+        <v>0.18</v>
       </c>
       <c r="I279" s="14" t="inlineStr">
         <is>
@@ -14757,7 +14757,7 @@
         </is>
       </c>
       <c r="H280" s="11" t="n">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="I280" s="11" t="inlineStr">
         <is>
@@ -14807,7 +14807,7 @@
         </is>
       </c>
       <c r="H281" s="14" t="n">
-        <v>0.39</v>
+        <v>0.42</v>
       </c>
       <c r="I281" s="14" t="inlineStr">
         <is>
@@ -14857,7 +14857,7 @@
         </is>
       </c>
       <c r="H282" s="11" t="n">
-        <v>0.43</v>
+        <v>0.26</v>
       </c>
       <c r="I282" s="11" t="inlineStr">
         <is>
@@ -14907,7 +14907,7 @@
         </is>
       </c>
       <c r="H283" s="14" t="n">
-        <v>0.26</v>
+        <v>0.12</v>
       </c>
       <c r="I283" s="14" t="inlineStr">
         <is>
@@ -14957,7 +14957,7 @@
         </is>
       </c>
       <c r="H284" s="11" t="n">
-        <v>0.21</v>
+        <v>0.19</v>
       </c>
       <c r="I284" s="11" t="inlineStr">
         <is>
@@ -15007,7 +15007,7 @@
         </is>
       </c>
       <c r="H285" s="14" t="n">
-        <v>0.27</v>
+        <v>0.13</v>
       </c>
       <c r="I285" s="14" t="inlineStr">
         <is>
@@ -15057,7 +15057,7 @@
         </is>
       </c>
       <c r="H286" s="11" t="n">
-        <v>0.38</v>
+        <v>0.23</v>
       </c>
       <c r="I286" s="11" t="inlineStr">
         <is>
@@ -15107,7 +15107,7 @@
         </is>
       </c>
       <c r="H287" s="14" t="n">
-        <v>0.18</v>
+        <v>0.37</v>
       </c>
       <c r="I287" s="14" t="inlineStr">
         <is>
@@ -15157,7 +15157,7 @@
         </is>
       </c>
       <c r="H288" s="11" t="n">
-        <v>0.35</v>
+        <v>0.31</v>
       </c>
       <c r="I288" s="11" t="inlineStr">
         <is>
@@ -15207,7 +15207,7 @@
         </is>
       </c>
       <c r="H289" s="14" t="n">
-        <v>0.42</v>
+        <v>0.26</v>
       </c>
       <c r="I289" s="14" t="inlineStr">
         <is>
@@ -15257,7 +15257,7 @@
         </is>
       </c>
       <c r="H290" s="11" t="n">
-        <v>0.22</v>
+        <v>0.4</v>
       </c>
       <c r="I290" s="11" t="inlineStr">
         <is>
@@ -15307,7 +15307,7 @@
         </is>
       </c>
       <c r="H291" s="14" t="n">
-        <v>0.32</v>
+        <v>0.4</v>
       </c>
       <c r="I291" s="14" t="inlineStr">
         <is>
@@ -15357,7 +15357,7 @@
         </is>
       </c>
       <c r="H292" s="11" t="n">
-        <v>0.24</v>
+        <v>0.44</v>
       </c>
       <c r="I292" s="11" t="inlineStr">
         <is>
@@ -15407,7 +15407,7 @@
         </is>
       </c>
       <c r="H293" s="14" t="n">
-        <v>0.19</v>
+        <v>0.42</v>
       </c>
       <c r="I293" s="14" t="inlineStr">
         <is>
@@ -15457,7 +15457,7 @@
         </is>
       </c>
       <c r="H294" s="11" t="n">
-        <v>0.34</v>
+        <v>0.37</v>
       </c>
       <c r="I294" s="11" t="inlineStr">
         <is>
@@ -15507,7 +15507,7 @@
         </is>
       </c>
       <c r="H295" s="14" t="n">
-        <v>0.15</v>
+        <v>0.25</v>
       </c>
       <c r="I295" s="14" t="inlineStr">
         <is>
@@ -15557,7 +15557,7 @@
         </is>
       </c>
       <c r="H296" s="11" t="n">
-        <v>0.12</v>
+        <v>0.33</v>
       </c>
       <c r="I296" s="11" t="inlineStr">
         <is>
@@ -15607,7 +15607,7 @@
         </is>
       </c>
       <c r="H297" s="14" t="n">
-        <v>0.13</v>
+        <v>0.44</v>
       </c>
       <c r="I297" s="14" t="inlineStr">
         <is>
@@ -15657,7 +15657,7 @@
         </is>
       </c>
       <c r="H298" s="11" t="n">
-        <v>0.25</v>
+        <v>0.11</v>
       </c>
       <c r="I298" s="11" t="inlineStr">
         <is>
@@ -15707,7 +15707,7 @@
         </is>
       </c>
       <c r="H299" s="14" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="I299" s="14" t="inlineStr">
         <is>
@@ -15757,7 +15757,7 @@
         </is>
       </c>
       <c r="H300" s="11" t="n">
-        <v>0.4</v>
+        <v>0.22</v>
       </c>
       <c r="I300" s="11" t="inlineStr">
         <is>
@@ -15857,7 +15857,7 @@
         </is>
       </c>
       <c r="H302" s="11" t="n">
-        <v>0.28</v>
+        <v>0.3</v>
       </c>
       <c r="I302" s="11" t="inlineStr">
         <is>
@@ -15907,7 +15907,7 @@
         </is>
       </c>
       <c r="H303" s="14" t="n">
-        <v>0.33</v>
+        <v>0.44</v>
       </c>
       <c r="I303" s="14" t="inlineStr">
         <is>
@@ -15957,7 +15957,7 @@
         </is>
       </c>
       <c r="H304" s="11" t="n">
-        <v>0.27</v>
+        <v>0.41</v>
       </c>
       <c r="I304" s="11" t="inlineStr">
         <is>
@@ -16007,7 +16007,7 @@
         </is>
       </c>
       <c r="H305" s="14" t="n">
-        <v>0.16</v>
+        <v>0.32</v>
       </c>
       <c r="I305" s="14" t="inlineStr">
         <is>
@@ -16057,7 +16057,7 @@
         </is>
       </c>
       <c r="H306" s="11" t="n">
-        <v>0.44</v>
+        <v>0.42</v>
       </c>
       <c r="I306" s="11" t="inlineStr">
         <is>
@@ -16107,7 +16107,7 @@
         </is>
       </c>
       <c r="H307" s="14" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="I307" s="14" t="inlineStr">
         <is>
@@ -16157,7 +16157,7 @@
         </is>
       </c>
       <c r="H308" s="11" t="n">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="I308" s="11" t="inlineStr">
         <is>
@@ -16207,7 +16207,7 @@
         </is>
       </c>
       <c r="H309" s="14" t="n">
-        <v>0.08</v>
+        <v>0.42</v>
       </c>
       <c r="I309" s="14" t="inlineStr">
         <is>
@@ -16257,7 +16257,7 @@
         </is>
       </c>
       <c r="H310" s="11" t="n">
-        <v>0.18</v>
+        <v>0.39</v>
       </c>
       <c r="I310" s="11" t="inlineStr">
         <is>
@@ -16307,7 +16307,7 @@
         </is>
       </c>
       <c r="H311" s="14" t="n">
-        <v>0.35</v>
+        <v>0.31</v>
       </c>
       <c r="I311" s="14" t="inlineStr">
         <is>
@@ -16357,7 +16357,7 @@
         </is>
       </c>
       <c r="H312" s="11" t="n">
-        <v>0.2</v>
+        <v>0.26</v>
       </c>
       <c r="I312" s="11" t="inlineStr">
         <is>
@@ -16407,7 +16407,7 @@
         </is>
       </c>
       <c r="H313" s="14" t="n">
-        <v>0.05</v>
+        <v>0.26</v>
       </c>
       <c r="I313" s="14" t="inlineStr">
         <is>
@@ -16457,7 +16457,7 @@
         </is>
       </c>
       <c r="H314" s="11" t="n">
-        <v>0.39</v>
+        <v>0.16</v>
       </c>
       <c r="I314" s="11" t="inlineStr">
         <is>
@@ -16507,7 +16507,7 @@
         </is>
       </c>
       <c r="H315" s="14" t="n">
-        <v>0.06</v>
+        <v>0.15</v>
       </c>
       <c r="I315" s="14" t="inlineStr">
         <is>
@@ -16557,7 +16557,7 @@
         </is>
       </c>
       <c r="H316" s="11" t="n">
-        <v>0.11</v>
+        <v>0.19</v>
       </c>
       <c r="I316" s="11" t="inlineStr">
         <is>
@@ -16607,7 +16607,7 @@
         </is>
       </c>
       <c r="H317" s="14" t="n">
-        <v>0.06</v>
+        <v>0.3</v>
       </c>
       <c r="I317" s="14" t="inlineStr">
         <is>
@@ -16657,7 +16657,7 @@
         </is>
       </c>
       <c r="H318" s="11" t="n">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="I318" s="11" t="inlineStr">
         <is>
@@ -16707,7 +16707,7 @@
         </is>
       </c>
       <c r="H319" s="14" t="n">
-        <v>0.08</v>
+        <v>0.36</v>
       </c>
       <c r="I319" s="14" t="inlineStr">
         <is>
@@ -16757,7 +16757,7 @@
         </is>
       </c>
       <c r="H320" s="11" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.31</v>
       </c>
       <c r="I320" s="11" t="inlineStr">
         <is>
@@ -16807,7 +16807,7 @@
         </is>
       </c>
       <c r="H321" s="14" t="n">
-        <v>0.43</v>
+        <v>0.3</v>
       </c>
       <c r="I321" s="14" t="inlineStr">
         <is>
@@ -16857,7 +16857,7 @@
         </is>
       </c>
       <c r="H322" s="11" t="n">
-        <v>0.25</v>
+        <v>0.27</v>
       </c>
       <c r="I322" s="11" t="inlineStr">
         <is>
@@ -16907,7 +16907,7 @@
         </is>
       </c>
       <c r="H323" s="14" t="n">
-        <v>0.37</v>
+        <v>0.4</v>
       </c>
       <c r="I323" s="14" t="inlineStr">
         <is>
@@ -16957,7 +16957,7 @@
         </is>
       </c>
       <c r="H324" s="11" t="n">
-        <v>0.11</v>
+        <v>0.28</v>
       </c>
       <c r="I324" s="11" t="inlineStr">
         <is>
@@ -17007,7 +17007,7 @@
         </is>
       </c>
       <c r="H325" s="14" t="n">
-        <v>0.3</v>
+        <v>0.16</v>
       </c>
       <c r="I325" s="14" t="inlineStr">
         <is>
@@ -17057,7 +17057,7 @@
         </is>
       </c>
       <c r="H326" s="11" t="n">
-        <v>0.35</v>
+        <v>0.34</v>
       </c>
       <c r="I326" s="11" t="inlineStr">
         <is>
@@ -17185,7 +17185,7 @@
         </is>
       </c>
       <c r="H2" s="17" t="n">
-        <v>0.18</v>
+        <v>0.26</v>
       </c>
       <c r="I2" s="17" t="inlineStr">
         <is>
@@ -17235,7 +17235,7 @@
         </is>
       </c>
       <c r="H3" s="18" t="n">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="I3" s="18" t="inlineStr">
         <is>
@@ -17285,7 +17285,7 @@
         </is>
       </c>
       <c r="H4" s="17" t="n">
-        <v>0.36</v>
+        <v>0.41</v>
       </c>
       <c r="I4" s="17" t="inlineStr">
         <is>
@@ -17335,7 +17335,7 @@
         </is>
       </c>
       <c r="H5" s="18" t="n">
-        <v>0.39</v>
+        <v>0.16</v>
       </c>
       <c r="I5" s="18" t="inlineStr">
         <is>
@@ -17385,7 +17385,7 @@
         </is>
       </c>
       <c r="H6" s="17" t="n">
-        <v>0.14</v>
+        <v>0.09</v>
       </c>
       <c r="I6" s="17" t="inlineStr">
         <is>
@@ -17485,7 +17485,7 @@
         </is>
       </c>
       <c r="H8" s="17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.17</v>
       </c>
       <c r="I8" s="17" t="inlineStr">
         <is>
@@ -17535,7 +17535,7 @@
         </is>
       </c>
       <c r="H9" s="18" t="n">
-        <v>0.32</v>
+        <v>0.11</v>
       </c>
       <c r="I9" s="18" t="inlineStr">
         <is>
@@ -17585,7 +17585,7 @@
         </is>
       </c>
       <c r="H10" s="17" t="n">
-        <v>0.1</v>
+        <v>0.31</v>
       </c>
       <c r="I10" s="17" t="inlineStr">
         <is>
@@ -17635,7 +17635,7 @@
         </is>
       </c>
       <c r="H11" s="18" t="n">
-        <v>0.27</v>
+        <v>0.12</v>
       </c>
       <c r="I11" s="18" t="inlineStr">
         <is>
@@ -17685,7 +17685,7 @@
         </is>
       </c>
       <c r="H12" s="17" t="n">
-        <v>0.18</v>
+        <v>0.39</v>
       </c>
       <c r="I12" s="17" t="inlineStr">
         <is>
@@ -17735,7 +17735,7 @@
         </is>
       </c>
       <c r="H13" s="18" t="n">
-        <v>0.41</v>
+        <v>0.34</v>
       </c>
       <c r="I13" s="18" t="inlineStr">
         <is>
@@ -17785,7 +17785,7 @@
         </is>
       </c>
       <c r="H14" s="17" t="n">
-        <v>0.19</v>
+        <v>0.06</v>
       </c>
       <c r="I14" s="17" t="inlineStr">
         <is>
@@ -17835,7 +17835,7 @@
         </is>
       </c>
       <c r="H15" s="18" t="n">
-        <v>0.25</v>
+        <v>0.32</v>
       </c>
       <c r="I15" s="18" t="inlineStr">
         <is>
@@ -17885,7 +17885,7 @@
         </is>
       </c>
       <c r="H16" s="17" t="n">
-        <v>0.19</v>
+        <v>0.3</v>
       </c>
       <c r="I16" s="17" t="inlineStr">
         <is>
@@ -17935,7 +17935,7 @@
         </is>
       </c>
       <c r="H17" s="18" t="n">
-        <v>0.2</v>
+        <v>0.16</v>
       </c>
       <c r="I17" s="18" t="inlineStr">
         <is>
@@ -17985,7 +17985,7 @@
         </is>
       </c>
       <c r="H18" s="17" t="n">
-        <v>0.23</v>
+        <v>0.35</v>
       </c>
       <c r="I18" s="17" t="inlineStr">
         <is>
@@ -18085,7 +18085,7 @@
         </is>
       </c>
       <c r="H20" s="17" t="n">
-        <v>0.39</v>
+        <v>0.32</v>
       </c>
       <c r="I20" s="17" t="inlineStr">
         <is>
@@ -18135,7 +18135,7 @@
         </is>
       </c>
       <c r="H21" s="18" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="I21" s="18" t="inlineStr">
         <is>
@@ -18185,7 +18185,7 @@
         </is>
       </c>
       <c r="H22" s="17" t="n">
-        <v>0.06</v>
+        <v>0.31</v>
       </c>
       <c r="I22" s="17" t="inlineStr">
         <is>
@@ -18235,7 +18235,7 @@
         </is>
       </c>
       <c r="H23" s="18" t="n">
-        <v>0.09</v>
+        <v>0.15</v>
       </c>
       <c r="I23" s="18" t="inlineStr">
         <is>
@@ -18285,7 +18285,7 @@
         </is>
       </c>
       <c r="H24" s="17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.24</v>
       </c>
       <c r="I24" s="17" t="inlineStr">
         <is>
@@ -18335,7 +18335,7 @@
         </is>
       </c>
       <c r="H25" s="18" t="n">
-        <v>0.26</v>
+        <v>0.41</v>
       </c>
       <c r="I25" s="18" t="inlineStr">
         <is>
@@ -18385,7 +18385,7 @@
         </is>
       </c>
       <c r="H26" s="17" t="n">
-        <v>0.34</v>
+        <v>0.16</v>
       </c>
       <c r="I26" s="17" t="inlineStr">
         <is>
@@ -18435,7 +18435,7 @@
         </is>
       </c>
       <c r="H27" s="18" t="n">
-        <v>0.29</v>
+        <v>0.21</v>
       </c>
       <c r="I27" s="18" t="inlineStr">
         <is>
@@ -18485,7 +18485,7 @@
         </is>
       </c>
       <c r="H28" s="17" t="n">
-        <v>0.14</v>
+        <v>0.05</v>
       </c>
       <c r="I28" s="17" t="inlineStr">
         <is>
@@ -18585,7 +18585,7 @@
         </is>
       </c>
       <c r="H30" s="17" t="n">
-        <v>0.29</v>
+        <v>0.24</v>
       </c>
       <c r="I30" s="17" t="inlineStr">
         <is>
@@ -18635,7 +18635,7 @@
         </is>
       </c>
       <c r="H31" s="18" t="n">
-        <v>0.39</v>
+        <v>0.08</v>
       </c>
       <c r="I31" s="18" t="inlineStr">
         <is>
@@ -18735,7 +18735,7 @@
         </is>
       </c>
       <c r="H33" s="18" t="n">
-        <v>0.1</v>
+        <v>0.19</v>
       </c>
       <c r="I33" s="18" t="inlineStr">
         <is>
@@ -18785,7 +18785,7 @@
         </is>
       </c>
       <c r="H34" s="17" t="n">
-        <v>0.22</v>
+        <v>0.08</v>
       </c>
       <c r="I34" s="17" t="inlineStr">
         <is>
@@ -18835,7 +18835,7 @@
         </is>
       </c>
       <c r="H35" s="18" t="n">
-        <v>0.08</v>
+        <v>0.16</v>
       </c>
       <c r="I35" s="18" t="inlineStr">
         <is>
@@ -18935,7 +18935,7 @@
         </is>
       </c>
       <c r="H37" s="18" t="n">
-        <v>0.2</v>
+        <v>0.13</v>
       </c>
       <c r="I37" s="18" t="inlineStr">
         <is>
@@ -18985,7 +18985,7 @@
         </is>
       </c>
       <c r="H38" s="17" t="n">
-        <v>0.14</v>
+        <v>0.27</v>
       </c>
       <c r="I38" s="17" t="inlineStr">
         <is>
@@ -19035,7 +19035,7 @@
         </is>
       </c>
       <c r="H39" s="18" t="n">
-        <v>0.25</v>
+        <v>0.42</v>
       </c>
       <c r="I39" s="18" t="inlineStr">
         <is>
@@ -19085,7 +19085,7 @@
         </is>
       </c>
       <c r="H40" s="17" t="n">
-        <v>0.2</v>
+        <v>0.29</v>
       </c>
       <c r="I40" s="17" t="inlineStr">
         <is>
@@ -19135,7 +19135,7 @@
         </is>
       </c>
       <c r="H41" s="18" t="n">
-        <v>0.21</v>
+        <v>0.25</v>
       </c>
       <c r="I41" s="18" t="inlineStr">
         <is>
@@ -19185,7 +19185,7 @@
         </is>
       </c>
       <c r="H42" s="17" t="n">
-        <v>0.1</v>
+        <v>0.14</v>
       </c>
       <c r="I42" s="17" t="inlineStr">
         <is>
@@ -19235,7 +19235,7 @@
         </is>
       </c>
       <c r="H43" s="18" t="n">
-        <v>0.12</v>
+        <v>0.42</v>
       </c>
       <c r="I43" s="18" t="inlineStr">
         <is>
@@ -19285,7 +19285,7 @@
         </is>
       </c>
       <c r="H44" s="17" t="n">
-        <v>0.31</v>
+        <v>0.08</v>
       </c>
       <c r="I44" s="17" t="inlineStr">
         <is>
@@ -19335,7 +19335,7 @@
         </is>
       </c>
       <c r="H45" s="18" t="n">
-        <v>0.43</v>
+        <v>0.19</v>
       </c>
       <c r="I45" s="18" t="inlineStr">
         <is>
@@ -19385,7 +19385,7 @@
         </is>
       </c>
       <c r="H46" s="17" t="n">
-        <v>0.31</v>
+        <v>0.24</v>
       </c>
       <c r="I46" s="17" t="inlineStr">
         <is>
@@ -19435,7 +19435,7 @@
         </is>
       </c>
       <c r="H47" s="18" t="n">
-        <v>0.27</v>
+        <v>0.38</v>
       </c>
       <c r="I47" s="18" t="inlineStr">
         <is>
@@ -19485,7 +19485,7 @@
         </is>
       </c>
       <c r="H48" s="17" t="n">
-        <v>0.26</v>
+        <v>0.37</v>
       </c>
       <c r="I48" s="17" t="inlineStr">
         <is>
@@ -19535,7 +19535,7 @@
         </is>
       </c>
       <c r="H49" s="18" t="n">
-        <v>0.27</v>
+        <v>0.16</v>
       </c>
       <c r="I49" s="18" t="inlineStr">
         <is>
@@ -19585,7 +19585,7 @@
         </is>
       </c>
       <c r="H50" s="17" t="n">
-        <v>0.39</v>
+        <v>0.38</v>
       </c>
       <c r="I50" s="17" t="inlineStr">
         <is>
@@ -19635,7 +19635,7 @@
         </is>
       </c>
       <c r="H51" s="18" t="n">
-        <v>0.23</v>
+        <v>0.37</v>
       </c>
       <c r="I51" s="18" t="inlineStr">
         <is>
@@ -19685,7 +19685,7 @@
         </is>
       </c>
       <c r="H52" s="17" t="n">
-        <v>0.42</v>
+        <v>0.32</v>
       </c>
       <c r="I52" s="17" t="inlineStr">
         <is>
@@ -19735,7 +19735,7 @@
         </is>
       </c>
       <c r="H53" s="18" t="n">
-        <v>0.39</v>
+        <v>0.25</v>
       </c>
       <c r="I53" s="18" t="inlineStr">
         <is>
@@ -19785,7 +19785,7 @@
         </is>
       </c>
       <c r="H54" s="17" t="n">
-        <v>0.25</v>
+        <v>0.11</v>
       </c>
       <c r="I54" s="17" t="inlineStr">
         <is>
@@ -19835,7 +19835,7 @@
         </is>
       </c>
       <c r="H55" s="18" t="n">
-        <v>0.35</v>
+        <v>0.21</v>
       </c>
       <c r="I55" s="18" t="inlineStr">
         <is>
@@ -19885,7 +19885,7 @@
         </is>
       </c>
       <c r="H56" s="17" t="n">
-        <v>0.4</v>
+        <v>0.39</v>
       </c>
       <c r="I56" s="17" t="inlineStr">
         <is>
@@ -19935,7 +19935,7 @@
         </is>
       </c>
       <c r="H57" s="18" t="n">
-        <v>0.14</v>
+        <v>0.16</v>
       </c>
       <c r="I57" s="18" t="inlineStr">
         <is>
@@ -19985,7 +19985,7 @@
         </is>
       </c>
       <c r="H58" s="17" t="n">
-        <v>0.25</v>
+        <v>0.32</v>
       </c>
       <c r="I58" s="17" t="inlineStr">
         <is>
@@ -20035,7 +20035,7 @@
         </is>
       </c>
       <c r="H59" s="18" t="n">
-        <v>0.08</v>
+        <v>0.34</v>
       </c>
       <c r="I59" s="18" t="inlineStr">
         <is>
@@ -20085,7 +20085,7 @@
         </is>
       </c>
       <c r="H60" s="17" t="n">
-        <v>0.38</v>
+        <v>0.4</v>
       </c>
       <c r="I60" s="17" t="inlineStr">
         <is>
@@ -20135,7 +20135,7 @@
         </is>
       </c>
       <c r="H61" s="18" t="n">
-        <v>0.2</v>
+        <v>0.34</v>
       </c>
       <c r="I61" s="18" t="inlineStr">
         <is>
@@ -20185,7 +20185,7 @@
         </is>
       </c>
       <c r="H62" s="17" t="n">
-        <v>0.39</v>
+        <v>0.08</v>
       </c>
       <c r="I62" s="17" t="inlineStr">
         <is>
@@ -20235,7 +20235,7 @@
         </is>
       </c>
       <c r="H63" s="18" t="n">
-        <v>0.23</v>
+        <v>0.1</v>
       </c>
       <c r="I63" s="18" t="inlineStr">
         <is>
@@ -20285,7 +20285,7 @@
         </is>
       </c>
       <c r="H64" s="17" t="n">
-        <v>0.28</v>
+        <v>0.05</v>
       </c>
       <c r="I64" s="17" t="inlineStr">
         <is>
@@ -20335,7 +20335,7 @@
         </is>
       </c>
       <c r="H65" s="18" t="n">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="I65" s="18" t="inlineStr">
         <is>
@@ -20385,7 +20385,7 @@
         </is>
       </c>
       <c r="H66" s="17" t="n">
-        <v>0.24</v>
+        <v>0.18</v>
       </c>
       <c r="I66" s="17" t="inlineStr">
         <is>
@@ -20435,7 +20435,7 @@
         </is>
       </c>
       <c r="H67" s="18" t="n">
-        <v>0.32</v>
+        <v>0.21</v>
       </c>
       <c r="I67" s="18" t="inlineStr">
         <is>
@@ -20485,7 +20485,7 @@
         </is>
       </c>
       <c r="H68" s="17" t="n">
-        <v>0.14</v>
+        <v>0.1</v>
       </c>
       <c r="I68" s="17" t="inlineStr">
         <is>
@@ -20535,7 +20535,7 @@
         </is>
       </c>
       <c r="H69" s="18" t="n">
-        <v>0.38</v>
+        <v>0.27</v>
       </c>
       <c r="I69" s="18" t="inlineStr">
         <is>
@@ -20585,7 +20585,7 @@
         </is>
       </c>
       <c r="H70" s="17" t="n">
-        <v>0.15</v>
+        <v>0.26</v>
       </c>
       <c r="I70" s="17" t="inlineStr">
         <is>
@@ -20635,7 +20635,7 @@
         </is>
       </c>
       <c r="H71" s="18" t="n">
-        <v>0.26</v>
+        <v>0.3</v>
       </c>
       <c r="I71" s="18" t="inlineStr">
         <is>
@@ -20685,7 +20685,7 @@
         </is>
       </c>
       <c r="H72" s="17" t="n">
-        <v>0.06</v>
+        <v>0.18</v>
       </c>
       <c r="I72" s="17" t="inlineStr">
         <is>
@@ -20735,7 +20735,7 @@
         </is>
       </c>
       <c r="H73" s="18" t="n">
-        <v>0.18</v>
+        <v>0.36</v>
       </c>
       <c r="I73" s="18" t="inlineStr">
         <is>
@@ -20785,7 +20785,7 @@
         </is>
       </c>
       <c r="H74" s="17" t="n">
-        <v>0.08</v>
+        <v>0.12</v>
       </c>
       <c r="I74" s="17" t="inlineStr">
         <is>
@@ -20835,7 +20835,7 @@
         </is>
       </c>
       <c r="H75" s="18" t="n">
-        <v>0.18</v>
+        <v>0.38</v>
       </c>
       <c r="I75" s="18" t="inlineStr">
         <is>
@@ -20885,7 +20885,7 @@
         </is>
       </c>
       <c r="H76" s="17" t="n">
-        <v>0.08</v>
+        <v>0.33</v>
       </c>
       <c r="I76" s="17" t="inlineStr">
         <is>
@@ -20935,7 +20935,7 @@
         </is>
       </c>
       <c r="H77" s="18" t="n">
-        <v>0.32</v>
+        <v>0.38</v>
       </c>
       <c r="I77" s="18" t="inlineStr">
         <is>
@@ -20985,7 +20985,7 @@
         </is>
       </c>
       <c r="H78" s="17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="I78" s="17" t="inlineStr">
         <is>
@@ -21085,7 +21085,7 @@
         </is>
       </c>
       <c r="H80" s="17" t="n">
-        <v>0.37</v>
+        <v>0.05</v>
       </c>
       <c r="I80" s="17" t="inlineStr">
         <is>
@@ -21135,7 +21135,7 @@
         </is>
       </c>
       <c r="H81" s="18" t="n">
-        <v>0.06</v>
+        <v>0.28</v>
       </c>
       <c r="I81" s="18" t="inlineStr">
         <is>
@@ -21185,7 +21185,7 @@
         </is>
       </c>
       <c r="H82" s="17" t="n">
-        <v>0.41</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I82" s="17" t="inlineStr">
         <is>
@@ -21235,7 +21235,7 @@
         </is>
       </c>
       <c r="H83" s="18" t="n">
-        <v>0.15</v>
+        <v>0.43</v>
       </c>
       <c r="I83" s="18" t="inlineStr">
         <is>
@@ -21285,7 +21285,7 @@
         </is>
       </c>
       <c r="H84" s="17" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="I84" s="17" t="inlineStr">
         <is>
@@ -21335,7 +21335,7 @@
         </is>
       </c>
       <c r="H85" s="18" t="n">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="I85" s="18" t="inlineStr">
         <is>
@@ -21385,7 +21385,7 @@
         </is>
       </c>
       <c r="H86" s="17" t="n">
-        <v>0.15</v>
+        <v>0.39</v>
       </c>
       <c r="I86" s="17" t="inlineStr">
         <is>
@@ -21435,7 +21435,7 @@
         </is>
       </c>
       <c r="H87" s="18" t="n">
-        <v>0.06</v>
+        <v>0.23</v>
       </c>
       <c r="I87" s="18" t="inlineStr">
         <is>
@@ -21485,7 +21485,7 @@
         </is>
       </c>
       <c r="H88" s="17" t="n">
-        <v>0.2</v>
+        <v>0.38</v>
       </c>
       <c r="I88" s="17" t="inlineStr">
         <is>
@@ -21535,7 +21535,7 @@
         </is>
       </c>
       <c r="H89" s="18" t="n">
-        <v>0.05</v>
+        <v>0.17</v>
       </c>
       <c r="I89" s="18" t="inlineStr">
         <is>
@@ -21585,7 +21585,7 @@
         </is>
       </c>
       <c r="H90" s="17" t="n">
-        <v>0.11</v>
+        <v>0.27</v>
       </c>
       <c r="I90" s="17" t="inlineStr">
         <is>
@@ -21635,7 +21635,7 @@
         </is>
       </c>
       <c r="H91" s="18" t="n">
-        <v>0.41</v>
+        <v>0.22</v>
       </c>
       <c r="I91" s="18" t="inlineStr">
         <is>
@@ -21685,7 +21685,7 @@
         </is>
       </c>
       <c r="H92" s="17" t="n">
-        <v>0.12</v>
+        <v>0.42</v>
       </c>
       <c r="I92" s="17" t="inlineStr">
         <is>
@@ -21735,7 +21735,7 @@
         </is>
       </c>
       <c r="H93" s="18" t="n">
-        <v>0.17</v>
+        <v>0.2</v>
       </c>
       <c r="I93" s="18" t="inlineStr">
         <is>
@@ -21785,7 +21785,7 @@
         </is>
       </c>
       <c r="H94" s="17" t="n">
-        <v>0.18</v>
+        <v>0.38</v>
       </c>
       <c r="I94" s="17" t="inlineStr">
         <is>
@@ -21835,7 +21835,7 @@
         </is>
       </c>
       <c r="H95" s="18" t="n">
-        <v>0.15</v>
+        <v>0.41</v>
       </c>
       <c r="I95" s="18" t="inlineStr">
         <is>
@@ -21885,7 +21885,7 @@
         </is>
       </c>
       <c r="H96" s="17" t="n">
-        <v>0.41</v>
+        <v>0.26</v>
       </c>
       <c r="I96" s="17" t="inlineStr">
         <is>
@@ -21935,7 +21935,7 @@
         </is>
       </c>
       <c r="H97" s="18" t="n">
-        <v>0.27</v>
+        <v>0.39</v>
       </c>
       <c r="I97" s="18" t="inlineStr">
         <is>
@@ -21985,7 +21985,7 @@
         </is>
       </c>
       <c r="H98" s="17" t="n">
-        <v>0.35</v>
+        <v>0.11</v>
       </c>
       <c r="I98" s="17" t="inlineStr">
         <is>
@@ -22035,7 +22035,7 @@
         </is>
       </c>
       <c r="H99" s="18" t="n">
-        <v>0.42</v>
+        <v>0.44</v>
       </c>
       <c r="I99" s="18" t="inlineStr">
         <is>
@@ -22085,7 +22085,7 @@
         </is>
       </c>
       <c r="H100" s="17" t="n">
-        <v>0.06</v>
+        <v>0.36</v>
       </c>
       <c r="I100" s="17" t="inlineStr">
         <is>
@@ -22135,7 +22135,7 @@
         </is>
       </c>
       <c r="H101" s="18" t="n">
-        <v>0.08</v>
+        <v>0.32</v>
       </c>
       <c r="I101" s="18" t="inlineStr">
         <is>
@@ -22185,7 +22185,7 @@
         </is>
       </c>
       <c r="H102" s="17" t="n">
-        <v>0.09</v>
+        <v>0.32</v>
       </c>
       <c r="I102" s="17" t="inlineStr">
         <is>
@@ -22235,7 +22235,7 @@
         </is>
       </c>
       <c r="H103" s="18" t="n">
-        <v>0.31</v>
+        <v>0.36</v>
       </c>
       <c r="I103" s="18" t="inlineStr">
         <is>
@@ -22285,7 +22285,7 @@
         </is>
       </c>
       <c r="H104" s="17" t="n">
-        <v>0.22</v>
+        <v>0.32</v>
       </c>
       <c r="I104" s="17" t="inlineStr">
         <is>
@@ -22335,7 +22335,7 @@
         </is>
       </c>
       <c r="H105" s="18" t="n">
-        <v>0.12</v>
+        <v>0.24</v>
       </c>
       <c r="I105" s="18" t="inlineStr">
         <is>
@@ -22385,7 +22385,7 @@
         </is>
       </c>
       <c r="H106" s="17" t="n">
-        <v>0.11</v>
+        <v>0.38</v>
       </c>
       <c r="I106" s="17" t="inlineStr">
         <is>
@@ -22435,7 +22435,7 @@
         </is>
       </c>
       <c r="H107" s="18" t="n">
-        <v>0.1</v>
+        <v>0.33</v>
       </c>
       <c r="I107" s="18" t="inlineStr">
         <is>
@@ -22485,7 +22485,7 @@
         </is>
       </c>
       <c r="H108" s="17" t="n">
-        <v>0.4</v>
+        <v>0.35</v>
       </c>
       <c r="I108" s="17" t="inlineStr">
         <is>
@@ -22535,7 +22535,7 @@
         </is>
       </c>
       <c r="H109" s="18" t="n">
-        <v>0.45</v>
+        <v>0.44</v>
       </c>
       <c r="I109" s="18" t="inlineStr">
         <is>
@@ -22585,7 +22585,7 @@
         </is>
       </c>
       <c r="H110" s="17" t="n">
-        <v>0.24</v>
+        <v>0.3</v>
       </c>
       <c r="I110" s="17" t="inlineStr">
         <is>
@@ -22635,7 +22635,7 @@
         </is>
       </c>
       <c r="H111" s="18" t="n">
-        <v>0.3</v>
+        <v>0.33</v>
       </c>
       <c r="I111" s="18" t="inlineStr">
         <is>
@@ -22685,7 +22685,7 @@
         </is>
       </c>
       <c r="H112" s="17" t="n">
-        <v>0.18</v>
+        <v>0.45</v>
       </c>
       <c r="I112" s="17" t="inlineStr">
         <is>
@@ -22735,7 +22735,7 @@
         </is>
       </c>
       <c r="H113" s="18" t="n">
-        <v>0.31</v>
+        <v>0.36</v>
       </c>
       <c r="I113" s="18" t="inlineStr">
         <is>
@@ -22785,7 +22785,7 @@
         </is>
       </c>
       <c r="H114" s="17" t="n">
-        <v>0.12</v>
+        <v>0.32</v>
       </c>
       <c r="I114" s="17" t="inlineStr">
         <is>
@@ -22835,7 +22835,7 @@
         </is>
       </c>
       <c r="H115" s="18" t="n">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="I115" s="18" t="inlineStr">
         <is>
@@ -22885,7 +22885,7 @@
         </is>
       </c>
       <c r="H116" s="17" t="n">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="I116" s="17" t="inlineStr">
         <is>
@@ -22935,7 +22935,7 @@
         </is>
       </c>
       <c r="H117" s="18" t="n">
-        <v>0.31</v>
+        <v>0.2</v>
       </c>
       <c r="I117" s="18" t="inlineStr">
         <is>
@@ -22985,7 +22985,7 @@
         </is>
       </c>
       <c r="H118" s="17" t="n">
-        <v>0.24</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I118" s="17" t="inlineStr">
         <is>
@@ -23035,7 +23035,7 @@
         </is>
       </c>
       <c r="H119" s="18" t="n">
-        <v>0.31</v>
+        <v>0.41</v>
       </c>
       <c r="I119" s="18" t="inlineStr">
         <is>
@@ -23085,7 +23085,7 @@
         </is>
       </c>
       <c r="H120" s="17" t="n">
-        <v>0.29</v>
+        <v>0.33</v>
       </c>
       <c r="I120" s="17" t="inlineStr">
         <is>
@@ -23135,7 +23135,7 @@
         </is>
       </c>
       <c r="H121" s="18" t="n">
-        <v>0.17</v>
+        <v>0.38</v>
       </c>
       <c r="I121" s="18" t="inlineStr">
         <is>
@@ -23185,7 +23185,7 @@
         </is>
       </c>
       <c r="H122" s="17" t="n">
-        <v>0.37</v>
+        <v>0.12</v>
       </c>
       <c r="I122" s="17" t="inlineStr">
         <is>
@@ -23235,7 +23235,7 @@
         </is>
       </c>
       <c r="H123" s="18" t="n">
-        <v>0.22</v>
+        <v>0.09</v>
       </c>
       <c r="I123" s="18" t="inlineStr">
         <is>
@@ -23285,7 +23285,7 @@
         </is>
       </c>
       <c r="H124" s="17" t="n">
-        <v>0.43</v>
+        <v>0.4</v>
       </c>
       <c r="I124" s="17" t="inlineStr">
         <is>
@@ -23335,7 +23335,7 @@
         </is>
       </c>
       <c r="H125" s="18" t="n">
-        <v>0.44</v>
+        <v>0.14</v>
       </c>
       <c r="I125" s="18" t="inlineStr">
         <is>
@@ -23385,7 +23385,7 @@
         </is>
       </c>
       <c r="H126" s="17" t="n">
-        <v>0.4</v>
+        <v>0.24</v>
       </c>
       <c r="I126" s="17" t="inlineStr">
         <is>
@@ -23435,7 +23435,7 @@
         </is>
       </c>
       <c r="H127" s="18" t="n">
-        <v>0.43</v>
+        <v>0.13</v>
       </c>
       <c r="I127" s="18" t="inlineStr">
         <is>
@@ -23485,7 +23485,7 @@
         </is>
       </c>
       <c r="H128" s="17" t="n">
-        <v>0.32</v>
+        <v>0.43</v>
       </c>
       <c r="I128" s="17" t="inlineStr">
         <is>
@@ -23535,7 +23535,7 @@
         </is>
       </c>
       <c r="H129" s="18" t="n">
-        <v>0.37</v>
+        <v>0.31</v>
       </c>
       <c r="I129" s="18" t="inlineStr">
         <is>
@@ -23585,7 +23585,7 @@
         </is>
       </c>
       <c r="H130" s="17" t="n">
-        <v>0.21</v>
+        <v>0.14</v>
       </c>
       <c r="I130" s="17" t="inlineStr">
         <is>
@@ -23635,7 +23635,7 @@
         </is>
       </c>
       <c r="H131" s="18" t="n">
-        <v>0.43</v>
+        <v>0.25</v>
       </c>
       <c r="I131" s="18" t="inlineStr">
         <is>
@@ -23685,7 +23685,7 @@
         </is>
       </c>
       <c r="H132" s="17" t="n">
-        <v>0.23</v>
+        <v>0.12</v>
       </c>
       <c r="I132" s="17" t="inlineStr">
         <is>
@@ -23735,7 +23735,7 @@
         </is>
       </c>
       <c r="H133" s="18" t="n">
-        <v>0.12</v>
+        <v>0.21</v>
       </c>
       <c r="I133" s="18" t="inlineStr">
         <is>
@@ -23785,7 +23785,7 @@
         </is>
       </c>
       <c r="H134" s="17" t="n">
-        <v>0.1</v>
+        <v>0.23</v>
       </c>
       <c r="I134" s="17" t="inlineStr">
         <is>
@@ -23835,7 +23835,7 @@
         </is>
       </c>
       <c r="H135" s="18" t="n">
-        <v>0.06</v>
+        <v>0.23</v>
       </c>
       <c r="I135" s="18" t="inlineStr">
         <is>
@@ -23885,7 +23885,7 @@
         </is>
       </c>
       <c r="H136" s="17" t="n">
-        <v>0.29</v>
+        <v>0.4</v>
       </c>
       <c r="I136" s="17" t="inlineStr">
         <is>
@@ -23935,7 +23935,7 @@
         </is>
       </c>
       <c r="H137" s="18" t="n">
-        <v>0.34</v>
+        <v>0.1</v>
       </c>
       <c r="I137" s="18" t="inlineStr">
         <is>
@@ -23985,7 +23985,7 @@
         </is>
       </c>
       <c r="H138" s="17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.25</v>
       </c>
       <c r="I138" s="17" t="inlineStr">
         <is>
@@ -24035,7 +24035,7 @@
         </is>
       </c>
       <c r="H139" s="18" t="n">
-        <v>0.21</v>
+        <v>0.08</v>
       </c>
       <c r="I139" s="18" t="inlineStr">
         <is>
@@ -24085,7 +24085,7 @@
         </is>
       </c>
       <c r="H140" s="17" t="n">
-        <v>0.4</v>
+        <v>0.17</v>
       </c>
       <c r="I140" s="17" t="inlineStr">
         <is>
@@ -24135,7 +24135,7 @@
         </is>
       </c>
       <c r="H141" s="18" t="n">
-        <v>0.05</v>
+        <v>0.3</v>
       </c>
       <c r="I141" s="18" t="inlineStr">
         <is>
@@ -24185,7 +24185,7 @@
         </is>
       </c>
       <c r="H142" s="17" t="n">
-        <v>0.27</v>
+        <v>0.37</v>
       </c>
       <c r="I142" s="17" t="inlineStr">
         <is>
@@ -24235,7 +24235,7 @@
         </is>
       </c>
       <c r="H143" s="18" t="n">
-        <v>0.4</v>
+        <v>0.15</v>
       </c>
       <c r="I143" s="18" t="inlineStr">
         <is>
@@ -24285,7 +24285,7 @@
         </is>
       </c>
       <c r="H144" s="17" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="I144" s="17" t="inlineStr">
         <is>
@@ -24335,7 +24335,7 @@
         </is>
       </c>
       <c r="H145" s="18" t="n">
-        <v>0.32</v>
+        <v>0.27</v>
       </c>
       <c r="I145" s="18" t="inlineStr">
         <is>
@@ -24385,7 +24385,7 @@
         </is>
       </c>
       <c r="H146" s="17" t="n">
-        <v>0.11</v>
+        <v>0.17</v>
       </c>
       <c r="I146" s="17" t="inlineStr">
         <is>
@@ -24435,7 +24435,7 @@
         </is>
       </c>
       <c r="H147" s="18" t="n">
-        <v>0.27</v>
+        <v>0.44</v>
       </c>
       <c r="I147" s="18" t="inlineStr">
         <is>
@@ -24485,7 +24485,7 @@
         </is>
       </c>
       <c r="H148" s="17" t="n">
-        <v>0.36</v>
+        <v>0.2</v>
       </c>
       <c r="I148" s="17" t="inlineStr">
         <is>
@@ -24535,7 +24535,7 @@
         </is>
       </c>
       <c r="H149" s="18" t="n">
-        <v>0.3</v>
+        <v>0.28</v>
       </c>
       <c r="I149" s="18" t="inlineStr">
         <is>
@@ -24585,7 +24585,7 @@
         </is>
       </c>
       <c r="H150" s="17" t="n">
-        <v>0.38</v>
+        <v>0.14</v>
       </c>
       <c r="I150" s="17" t="inlineStr">
         <is>
@@ -24635,7 +24635,7 @@
         </is>
       </c>
       <c r="H151" s="18" t="n">
-        <v>0.08</v>
+        <v>0.24</v>
       </c>
       <c r="I151" s="18" t="inlineStr">
         <is>
@@ -24735,7 +24735,7 @@
         </is>
       </c>
       <c r="H153" s="18" t="n">
-        <v>0.3</v>
+        <v>0.06</v>
       </c>
       <c r="I153" s="18" t="inlineStr">
         <is>
@@ -24785,7 +24785,7 @@
         </is>
       </c>
       <c r="H154" s="17" t="n">
-        <v>0.08</v>
+        <v>0.33</v>
       </c>
       <c r="I154" s="17" t="inlineStr">
         <is>
@@ -24835,7 +24835,7 @@
         </is>
       </c>
       <c r="H155" s="18" t="n">
-        <v>0.14</v>
+        <v>0.23</v>
       </c>
       <c r="I155" s="18" t="inlineStr">
         <is>
@@ -24885,7 +24885,7 @@
         </is>
       </c>
       <c r="H156" s="17" t="n">
-        <v>0.06</v>
+        <v>0.14</v>
       </c>
       <c r="I156" s="17" t="inlineStr">
         <is>
@@ -24935,7 +24935,7 @@
         </is>
       </c>
       <c r="H157" s="18" t="n">
-        <v>0.3</v>
+        <v>0.25</v>
       </c>
       <c r="I157" s="18" t="inlineStr">
         <is>
@@ -24985,7 +24985,7 @@
         </is>
       </c>
       <c r="H158" s="17" t="n">
-        <v>0.29</v>
+        <v>0.4</v>
       </c>
       <c r="I158" s="17" t="inlineStr">
         <is>
@@ -25035,7 +25035,7 @@
         </is>
       </c>
       <c r="H159" s="18" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.33</v>
       </c>
       <c r="I159" s="18" t="inlineStr">
         <is>
@@ -25085,7 +25085,7 @@
         </is>
       </c>
       <c r="H160" s="17" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="I160" s="17" t="inlineStr">
         <is>
@@ -25135,7 +25135,7 @@
         </is>
       </c>
       <c r="H161" s="18" t="n">
-        <v>0.38</v>
+        <v>0.37</v>
       </c>
       <c r="I161" s="18" t="inlineStr">
         <is>
@@ -25185,7 +25185,7 @@
         </is>
       </c>
       <c r="H162" s="17" t="n">
-        <v>0.44</v>
+        <v>0.21</v>
       </c>
       <c r="I162" s="17" t="inlineStr">
         <is>
@@ -25235,7 +25235,7 @@
         </is>
       </c>
       <c r="H163" s="18" t="n">
-        <v>0.24</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I163" s="18" t="inlineStr">
         <is>
@@ -25285,7 +25285,7 @@
         </is>
       </c>
       <c r="H164" s="17" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="I164" s="17" t="inlineStr">
         <is>
@@ -25335,7 +25335,7 @@
         </is>
       </c>
       <c r="H165" s="18" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.21</v>
       </c>
       <c r="I165" s="18" t="inlineStr">
         <is>
@@ -25385,7 +25385,7 @@
         </is>
       </c>
       <c r="H166" s="17" t="n">
-        <v>0.43</v>
+        <v>0.37</v>
       </c>
       <c r="I166" s="17" t="inlineStr">
         <is>
@@ -25435,7 +25435,7 @@
         </is>
       </c>
       <c r="H167" s="18" t="n">
-        <v>0.11</v>
+        <v>0.29</v>
       </c>
       <c r="I167" s="18" t="inlineStr">
         <is>
@@ -25485,7 +25485,7 @@
         </is>
       </c>
       <c r="H168" s="17" t="n">
-        <v>0.22</v>
+        <v>0.29</v>
       </c>
       <c r="I168" s="17" t="inlineStr">
         <is>
@@ -25585,7 +25585,7 @@
         </is>
       </c>
       <c r="H170" s="17" t="n">
-        <v>0.2</v>
+        <v>0.08</v>
       </c>
       <c r="I170" s="17" t="inlineStr">
         <is>
@@ -25635,7 +25635,7 @@
         </is>
       </c>
       <c r="H171" s="18" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="I171" s="18" t="inlineStr">
         <is>
@@ -25685,7 +25685,7 @@
         </is>
       </c>
       <c r="H172" s="17" t="n">
-        <v>0.15</v>
+        <v>0.4</v>
       </c>
       <c r="I172" s="17" t="inlineStr">
         <is>
@@ -25735,7 +25735,7 @@
         </is>
       </c>
       <c r="H173" s="18" t="n">
-        <v>0.41</v>
+        <v>0.19</v>
       </c>
       <c r="I173" s="18" t="inlineStr">
         <is>
@@ -25785,7 +25785,7 @@
         </is>
       </c>
       <c r="H174" s="17" t="n">
-        <v>0.37</v>
+        <v>0.33</v>
       </c>
       <c r="I174" s="17" t="inlineStr">
         <is>
@@ -25835,7 +25835,7 @@
         </is>
       </c>
       <c r="H175" s="18" t="n">
-        <v>0.23</v>
+        <v>0.37</v>
       </c>
       <c r="I175" s="18" t="inlineStr">
         <is>
@@ -25885,7 +25885,7 @@
         </is>
       </c>
       <c r="H176" s="17" t="n">
-        <v>0.28</v>
+        <v>0.24</v>
       </c>
       <c r="I176" s="17" t="inlineStr">
         <is>
@@ -25935,7 +25935,7 @@
         </is>
       </c>
       <c r="H177" s="18" t="n">
-        <v>0.12</v>
+        <v>0.43</v>
       </c>
       <c r="I177" s="18" t="inlineStr">
         <is>
@@ -25985,7 +25985,7 @@
         </is>
       </c>
       <c r="H178" s="17" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="I178" s="17" t="inlineStr">
         <is>
@@ -26035,7 +26035,7 @@
         </is>
       </c>
       <c r="H179" s="18" t="n">
-        <v>0.05</v>
+        <v>0.19</v>
       </c>
       <c r="I179" s="18" t="inlineStr">
         <is>
@@ -26085,7 +26085,7 @@
         </is>
       </c>
       <c r="H180" s="17" t="n">
-        <v>0.22</v>
+        <v>0.18</v>
       </c>
       <c r="I180" s="17" t="inlineStr">
         <is>
@@ -26135,7 +26135,7 @@
         </is>
       </c>
       <c r="H181" s="18" t="n">
-        <v>0.21</v>
+        <v>0.26</v>
       </c>
       <c r="I181" s="18" t="inlineStr">
         <is>
@@ -26185,7 +26185,7 @@
         </is>
       </c>
       <c r="H182" s="17" t="n">
-        <v>0.36</v>
+        <v>0.13</v>
       </c>
       <c r="I182" s="17" t="inlineStr">
         <is>
@@ -26235,7 +26235,7 @@
         </is>
       </c>
       <c r="H183" s="18" t="n">
-        <v>0.06</v>
+        <v>0.22</v>
       </c>
       <c r="I183" s="18" t="inlineStr">
         <is>
@@ -26285,7 +26285,7 @@
         </is>
       </c>
       <c r="H184" s="17" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="I184" s="17" t="inlineStr">
         <is>
@@ -26335,7 +26335,7 @@
         </is>
       </c>
       <c r="H185" s="18" t="n">
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="I185" s="18" t="inlineStr">
         <is>
@@ -26385,7 +26385,7 @@
         </is>
       </c>
       <c r="H186" s="17" t="n">
-        <v>0.32</v>
+        <v>0.14</v>
       </c>
       <c r="I186" s="17" t="inlineStr">
         <is>
@@ -26435,7 +26435,7 @@
         </is>
       </c>
       <c r="H187" s="18" t="n">
-        <v>0.32</v>
+        <v>0.29</v>
       </c>
       <c r="I187" s="18" t="inlineStr">
         <is>
@@ -26485,7 +26485,7 @@
         </is>
       </c>
       <c r="H188" s="17" t="n">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="I188" s="17" t="inlineStr">
         <is>
@@ -26585,7 +26585,7 @@
         </is>
       </c>
       <c r="H190" s="17" t="n">
-        <v>0.28</v>
+        <v>0.2</v>
       </c>
       <c r="I190" s="17" t="inlineStr">
         <is>
@@ -26635,7 +26635,7 @@
         </is>
       </c>
       <c r="H191" s="18" t="n">
-        <v>0.29</v>
+        <v>0.12</v>
       </c>
       <c r="I191" s="18" t="inlineStr">
         <is>
@@ -26685,7 +26685,7 @@
         </is>
       </c>
       <c r="H192" s="17" t="n">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
       <c r="I192" s="17" t="inlineStr">
         <is>
@@ -26735,7 +26735,7 @@
         </is>
       </c>
       <c r="H193" s="18" t="n">
-        <v>0.14</v>
+        <v>0.36</v>
       </c>
       <c r="I193" s="18" t="inlineStr">
         <is>
@@ -26785,7 +26785,7 @@
         </is>
       </c>
       <c r="H194" s="17" t="n">
-        <v>0.31</v>
+        <v>0.14</v>
       </c>
       <c r="I194" s="17" t="inlineStr">
         <is>
@@ -26835,7 +26835,7 @@
         </is>
       </c>
       <c r="H195" s="18" t="n">
-        <v>0.23</v>
+        <v>0.32</v>
       </c>
       <c r="I195" s="18" t="inlineStr">
         <is>
@@ -26885,7 +26885,7 @@
         </is>
       </c>
       <c r="H196" s="17" t="n">
-        <v>0.13</v>
+        <v>0.21</v>
       </c>
       <c r="I196" s="17" t="inlineStr">
         <is>
@@ -26935,7 +26935,7 @@
         </is>
       </c>
       <c r="H197" s="18" t="n">
-        <v>0.18</v>
+        <v>0.3</v>
       </c>
       <c r="I197" s="18" t="inlineStr">
         <is>
@@ -26985,7 +26985,7 @@
         </is>
       </c>
       <c r="H198" s="17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.17</v>
       </c>
       <c r="I198" s="17" t="inlineStr">
         <is>
@@ -27035,7 +27035,7 @@
         </is>
       </c>
       <c r="H199" s="18" t="n">
-        <v>0.16</v>
+        <v>0.39</v>
       </c>
       <c r="I199" s="18" t="inlineStr">
         <is>
@@ -27085,7 +27085,7 @@
         </is>
       </c>
       <c r="H200" s="17" t="n">
-        <v>0.06</v>
+        <v>0.18</v>
       </c>
       <c r="I200" s="17" t="inlineStr">
         <is>
@@ -27135,7 +27135,7 @@
         </is>
       </c>
       <c r="H201" s="18" t="n">
-        <v>0.22</v>
+        <v>0.39</v>
       </c>
       <c r="I201" s="18" t="inlineStr">
         <is>
@@ -27185,7 +27185,7 @@
         </is>
       </c>
       <c r="H202" s="17" t="n">
-        <v>0.37</v>
+        <v>0.23</v>
       </c>
       <c r="I202" s="17" t="inlineStr">
         <is>
@@ -27235,7 +27235,7 @@
         </is>
       </c>
       <c r="H203" s="18" t="n">
-        <v>0.26</v>
+        <v>0.17</v>
       </c>
       <c r="I203" s="18" t="inlineStr">
         <is>
@@ -27285,7 +27285,7 @@
         </is>
       </c>
       <c r="H204" s="17" t="n">
-        <v>0.34</v>
+        <v>0.06</v>
       </c>
       <c r="I204" s="17" t="inlineStr">
         <is>
@@ -27335,7 +27335,7 @@
         </is>
       </c>
       <c r="H205" s="18" t="n">
-        <v>0.27</v>
+        <v>0.23</v>
       </c>
       <c r="I205" s="18" t="inlineStr">
         <is>
@@ -27385,7 +27385,7 @@
         </is>
       </c>
       <c r="H206" s="17" t="n">
-        <v>0.35</v>
+        <v>0.27</v>
       </c>
       <c r="I206" s="17" t="inlineStr">
         <is>
@@ -27435,7 +27435,7 @@
         </is>
       </c>
       <c r="H207" s="18" t="n">
-        <v>0.31</v>
+        <v>0.2</v>
       </c>
       <c r="I207" s="18" t="inlineStr">
         <is>
@@ -27485,7 +27485,7 @@
         </is>
       </c>
       <c r="H208" s="17" t="n">
-        <v>0.18</v>
+        <v>0.41</v>
       </c>
       <c r="I208" s="17" t="inlineStr">
         <is>
@@ -27535,7 +27535,7 @@
         </is>
       </c>
       <c r="H209" s="18" t="n">
-        <v>0.35</v>
+        <v>0.16</v>
       </c>
       <c r="I209" s="18" t="inlineStr">
         <is>
@@ -27585,7 +27585,7 @@
         </is>
       </c>
       <c r="H210" s="17" t="n">
-        <v>0.42</v>
+        <v>0.16</v>
       </c>
       <c r="I210" s="17" t="inlineStr">
         <is>
@@ -27635,7 +27635,7 @@
         </is>
       </c>
       <c r="H211" s="18" t="n">
-        <v>0.34</v>
+        <v>0.26</v>
       </c>
       <c r="I211" s="18" t="inlineStr">
         <is>
@@ -27685,7 +27685,7 @@
         </is>
       </c>
       <c r="H212" s="17" t="n">
-        <v>0.41</v>
+        <v>0.4</v>
       </c>
       <c r="I212" s="17" t="inlineStr">
         <is>
@@ -27735,7 +27735,7 @@
         </is>
       </c>
       <c r="H213" s="18" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="I213" s="18" t="inlineStr">
         <is>
@@ -27835,7 +27835,7 @@
         </is>
       </c>
       <c r="H215" s="18" t="n">
-        <v>0.17</v>
+        <v>0.43</v>
       </c>
       <c r="I215" s="18" t="inlineStr">
         <is>
@@ -27885,7 +27885,7 @@
         </is>
       </c>
       <c r="H216" s="17" t="n">
-        <v>0.4</v>
+        <v>0.17</v>
       </c>
       <c r="I216" s="17" t="inlineStr">
         <is>
@@ -27935,7 +27935,7 @@
         </is>
       </c>
       <c r="H217" s="18" t="n">
-        <v>0.43</v>
+        <v>0.18</v>
       </c>
       <c r="I217" s="18" t="inlineStr">
         <is>
@@ -27985,7 +27985,7 @@
         </is>
       </c>
       <c r="H218" s="17" t="n">
-        <v>0.35</v>
+        <v>0.37</v>
       </c>
       <c r="I218" s="17" t="inlineStr">
         <is>
@@ -28035,7 +28035,7 @@
         </is>
       </c>
       <c r="H219" s="18" t="n">
-        <v>0.12</v>
+        <v>0.06</v>
       </c>
       <c r="I219" s="18" t="inlineStr">
         <is>
@@ -28085,7 +28085,7 @@
         </is>
       </c>
       <c r="H220" s="17" t="n">
-        <v>0.24</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I220" s="17" t="inlineStr">
         <is>
@@ -28135,7 +28135,7 @@
         </is>
       </c>
       <c r="H221" s="18" t="n">
-        <v>0.19</v>
+        <v>0.15</v>
       </c>
       <c r="I221" s="18" t="inlineStr">
         <is>
@@ -28185,7 +28185,7 @@
         </is>
       </c>
       <c r="H222" s="17" t="n">
-        <v>0.25</v>
+        <v>0.11</v>
       </c>
       <c r="I222" s="17" t="inlineStr">
         <is>
@@ -28235,7 +28235,7 @@
         </is>
       </c>
       <c r="H223" s="18" t="n">
-        <v>0.38</v>
+        <v>0.31</v>
       </c>
       <c r="I223" s="18" t="inlineStr">
         <is>
@@ -28285,7 +28285,7 @@
         </is>
       </c>
       <c r="H224" s="17" t="n">
-        <v>0.39</v>
+        <v>0.19</v>
       </c>
       <c r="I224" s="17" t="inlineStr">
         <is>
@@ -28335,7 +28335,7 @@
         </is>
       </c>
       <c r="H225" s="18" t="n">
-        <v>0.25</v>
+        <v>0.17</v>
       </c>
       <c r="I225" s="18" t="inlineStr">
         <is>
@@ -28385,7 +28385,7 @@
         </is>
       </c>
       <c r="H226" s="17" t="n">
-        <v>0.34</v>
+        <v>0.16</v>
       </c>
       <c r="I226" s="17" t="inlineStr">
         <is>
@@ -28435,7 +28435,7 @@
         </is>
       </c>
       <c r="H227" s="18" t="n">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="I227" s="18" t="inlineStr">
         <is>
@@ -28485,7 +28485,7 @@
         </is>
       </c>
       <c r="H228" s="17" t="n">
-        <v>0.18</v>
+        <v>0.13</v>
       </c>
       <c r="I228" s="17" t="inlineStr">
         <is>
@@ -28535,7 +28535,7 @@
         </is>
       </c>
       <c r="H229" s="18" t="n">
-        <v>0.18</v>
+        <v>0.12</v>
       </c>
       <c r="I229" s="18" t="inlineStr">
         <is>
@@ -28585,7 +28585,7 @@
         </is>
       </c>
       <c r="H230" s="17" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="I230" s="17" t="inlineStr">
         <is>
@@ -28635,7 +28635,7 @@
         </is>
       </c>
       <c r="H231" s="18" t="n">
-        <v>0.35</v>
+        <v>0.29</v>
       </c>
       <c r="I231" s="18" t="inlineStr">
         <is>
@@ -28685,7 +28685,7 @@
         </is>
       </c>
       <c r="H232" s="17" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="I232" s="17" t="inlineStr">
         <is>
@@ -28735,7 +28735,7 @@
         </is>
       </c>
       <c r="H233" s="18" t="n">
-        <v>0.36</v>
+        <v>0.11</v>
       </c>
       <c r="I233" s="18" t="inlineStr">
         <is>
@@ -28785,7 +28785,7 @@
         </is>
       </c>
       <c r="H234" s="17" t="n">
-        <v>0.37</v>
+        <v>0.13</v>
       </c>
       <c r="I234" s="17" t="inlineStr">
         <is>
@@ -28835,7 +28835,7 @@
         </is>
       </c>
       <c r="H235" s="18" t="n">
-        <v>0.22</v>
+        <v>0.19</v>
       </c>
       <c r="I235" s="18" t="inlineStr">
         <is>
@@ -28885,7 +28885,7 @@
         </is>
       </c>
       <c r="H236" s="17" t="n">
-        <v>0.45</v>
+        <v>0.29</v>
       </c>
       <c r="I236" s="17" t="inlineStr">
         <is>
@@ -28935,7 +28935,7 @@
         </is>
       </c>
       <c r="H237" s="18" t="n">
-        <v>0.44</v>
+        <v>0.28</v>
       </c>
       <c r="I237" s="18" t="inlineStr">
         <is>
@@ -28985,7 +28985,7 @@
         </is>
       </c>
       <c r="H238" s="17" t="n">
-        <v>0.09</v>
+        <v>0.29</v>
       </c>
       <c r="I238" s="17" t="inlineStr">
         <is>
@@ -29035,7 +29035,7 @@
         </is>
       </c>
       <c r="H239" s="18" t="n">
-        <v>0.27</v>
+        <v>0.44</v>
       </c>
       <c r="I239" s="18" t="inlineStr">
         <is>
@@ -29085,7 +29085,7 @@
         </is>
       </c>
       <c r="H240" s="17" t="n">
-        <v>0.08</v>
+        <v>0.24</v>
       </c>
       <c r="I240" s="17" t="inlineStr">
         <is>
@@ -29135,7 +29135,7 @@
         </is>
       </c>
       <c r="H241" s="18" t="n">
-        <v>0.33</v>
+        <v>0.06</v>
       </c>
       <c r="I241" s="18" t="inlineStr">
         <is>
@@ -29185,7 +29185,7 @@
         </is>
       </c>
       <c r="H242" s="17" t="n">
-        <v>0.2</v>
+        <v>0.11</v>
       </c>
       <c r="I242" s="17" t="inlineStr">
         <is>
@@ -29235,7 +29235,7 @@
         </is>
       </c>
       <c r="H243" s="18" t="n">
-        <v>0.26</v>
+        <v>0.13</v>
       </c>
       <c r="I243" s="18" t="inlineStr">
         <is>
@@ -29285,7 +29285,7 @@
         </is>
       </c>
       <c r="H244" s="17" t="n">
-        <v>0.39</v>
+        <v>0.41</v>
       </c>
       <c r="I244" s="17" t="inlineStr">
         <is>
@@ -29335,7 +29335,7 @@
         </is>
       </c>
       <c r="H245" s="18" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="I245" s="18" t="inlineStr">
         <is>
@@ -29385,7 +29385,7 @@
         </is>
       </c>
       <c r="H246" s="17" t="n">
-        <v>0.29</v>
+        <v>0.35</v>
       </c>
       <c r="I246" s="17" t="inlineStr">
         <is>
@@ -29435,7 +29435,7 @@
         </is>
       </c>
       <c r="H247" s="18" t="n">
-        <v>0.42</v>
+        <v>0.3</v>
       </c>
       <c r="I247" s="18" t="inlineStr">
         <is>
@@ -29485,7 +29485,7 @@
         </is>
       </c>
       <c r="H248" s="17" t="n">
-        <v>0.27</v>
+        <v>0.38</v>
       </c>
       <c r="I248" s="17" t="inlineStr">
         <is>
@@ -29535,7 +29535,7 @@
         </is>
       </c>
       <c r="H249" s="18" t="n">
-        <v>0.44</v>
+        <v>0.13</v>
       </c>
       <c r="I249" s="18" t="inlineStr">
         <is>
@@ -29585,7 +29585,7 @@
         </is>
       </c>
       <c r="H250" s="17" t="n">
-        <v>0.17</v>
+        <v>0.4</v>
       </c>
       <c r="I250" s="17" t="inlineStr">
         <is>
@@ -29635,7 +29635,7 @@
         </is>
       </c>
       <c r="H251" s="18" t="n">
-        <v>0.13</v>
+        <v>0.4</v>
       </c>
       <c r="I251" s="18" t="inlineStr">
         <is>
@@ -29685,7 +29685,7 @@
         </is>
       </c>
       <c r="H252" s="17" t="n">
-        <v>0.08</v>
+        <v>0.38</v>
       </c>
       <c r="I252" s="17" t="inlineStr">
         <is>
@@ -29735,7 +29735,7 @@
         </is>
       </c>
       <c r="H253" s="18" t="n">
-        <v>0.18</v>
+        <v>0.22</v>
       </c>
       <c r="I253" s="18" t="inlineStr">
         <is>
@@ -29785,7 +29785,7 @@
         </is>
       </c>
       <c r="H254" s="17" t="n">
-        <v>0.08</v>
+        <v>0.1</v>
       </c>
       <c r="I254" s="17" t="inlineStr">
         <is>
@@ -29835,7 +29835,7 @@
         </is>
       </c>
       <c r="H255" s="18" t="n">
-        <v>0.12</v>
+        <v>0.15</v>
       </c>
       <c r="I255" s="18" t="inlineStr">
         <is>
@@ -29885,7 +29885,7 @@
         </is>
       </c>
       <c r="H256" s="17" t="n">
-        <v>0.42</v>
+        <v>0.33</v>
       </c>
       <c r="I256" s="17" t="inlineStr">
         <is>
@@ -29935,7 +29935,7 @@
         </is>
       </c>
       <c r="H257" s="18" t="n">
-        <v>0.19</v>
+        <v>0.38</v>
       </c>
       <c r="I257" s="18" t="inlineStr">
         <is>
@@ -29985,7 +29985,7 @@
         </is>
       </c>
       <c r="H258" s="17" t="n">
-        <v>0.12</v>
+        <v>0.34</v>
       </c>
       <c r="I258" s="17" t="inlineStr">
         <is>
@@ -30035,7 +30035,7 @@
         </is>
       </c>
       <c r="H259" s="18" t="n">
-        <v>0.25</v>
+        <v>0.43</v>
       </c>
       <c r="I259" s="18" t="inlineStr">
         <is>
@@ -30085,7 +30085,7 @@
         </is>
       </c>
       <c r="H260" s="17" t="n">
-        <v>0.33</v>
+        <v>0.2</v>
       </c>
       <c r="I260" s="17" t="inlineStr">
         <is>
@@ -30135,7 +30135,7 @@
         </is>
       </c>
       <c r="H261" s="18" t="n">
-        <v>0.25</v>
+        <v>0.13</v>
       </c>
       <c r="I261" s="18" t="inlineStr">
         <is>
@@ -30185,7 +30185,7 @@
         </is>
       </c>
       <c r="H262" s="17" t="n">
-        <v>0.16</v>
+        <v>0.26</v>
       </c>
       <c r="I262" s="17" t="inlineStr">
         <is>
@@ -30235,7 +30235,7 @@
         </is>
       </c>
       <c r="H263" s="18" t="n">
-        <v>0.08</v>
+        <v>0.32</v>
       </c>
       <c r="I263" s="18" t="inlineStr">
         <is>
@@ -30285,7 +30285,7 @@
         </is>
       </c>
       <c r="H264" s="17" t="n">
-        <v>0.18</v>
+        <v>0.41</v>
       </c>
       <c r="I264" s="17" t="inlineStr">
         <is>
@@ -30335,7 +30335,7 @@
         </is>
       </c>
       <c r="H265" s="18" t="n">
-        <v>0.2</v>
+        <v>0.26</v>
       </c>
       <c r="I265" s="18" t="inlineStr">
         <is>
@@ -30385,7 +30385,7 @@
         </is>
       </c>
       <c r="H266" s="17" t="n">
-        <v>0.09</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I266" s="17" t="inlineStr">
         <is>
@@ -30435,7 +30435,7 @@
         </is>
       </c>
       <c r="H267" s="18" t="n">
-        <v>0.26</v>
+        <v>0.12</v>
       </c>
       <c r="I267" s="18" t="inlineStr">
         <is>
@@ -30485,7 +30485,7 @@
         </is>
       </c>
       <c r="H268" s="17" t="n">
-        <v>0.29</v>
+        <v>0.44</v>
       </c>
       <c r="I268" s="17" t="inlineStr">
         <is>
@@ -30535,7 +30535,7 @@
         </is>
       </c>
       <c r="H269" s="18" t="n">
-        <v>0.16</v>
+        <v>0.41</v>
       </c>
       <c r="I269" s="18" t="inlineStr">
         <is>
@@ -30585,7 +30585,7 @@
         </is>
       </c>
       <c r="H270" s="17" t="n">
-        <v>0.44</v>
+        <v>0.35</v>
       </c>
       <c r="I270" s="17" t="inlineStr">
         <is>
@@ -30635,7 +30635,7 @@
         </is>
       </c>
       <c r="H271" s="18" t="n">
-        <v>0.12</v>
+        <v>0.26</v>
       </c>
       <c r="I271" s="18" t="inlineStr">
         <is>
@@ -30685,7 +30685,7 @@
         </is>
       </c>
       <c r="H272" s="17" t="n">
-        <v>0.16</v>
+        <v>0.31</v>
       </c>
       <c r="I272" s="17" t="inlineStr">
         <is>
@@ -30735,7 +30735,7 @@
         </is>
       </c>
       <c r="H273" s="18" t="n">
-        <v>0.17</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I273" s="18" t="inlineStr">
         <is>
@@ -30785,7 +30785,7 @@
         </is>
       </c>
       <c r="H274" s="17" t="n">
-        <v>0.21</v>
+        <v>0.43</v>
       </c>
       <c r="I274" s="17" t="inlineStr">
         <is>
@@ -30835,7 +30835,7 @@
         </is>
       </c>
       <c r="H275" s="18" t="n">
-        <v>0.34</v>
+        <v>0.09</v>
       </c>
       <c r="I275" s="18" t="inlineStr">
         <is>
@@ -30885,7 +30885,7 @@
         </is>
       </c>
       <c r="H276" s="17" t="n">
-        <v>0.25</v>
+        <v>0.27</v>
       </c>
       <c r="I276" s="17" t="inlineStr">
         <is>
@@ -30935,7 +30935,7 @@
         </is>
       </c>
       <c r="H277" s="18" t="n">
-        <v>0.36</v>
+        <v>0.28</v>
       </c>
       <c r="I277" s="18" t="inlineStr">
         <is>
@@ -30985,7 +30985,7 @@
         </is>
       </c>
       <c r="H278" s="17" t="n">
-        <v>0.4</v>
+        <v>0.18</v>
       </c>
       <c r="I278" s="17" t="inlineStr">
         <is>
@@ -31035,7 +31035,7 @@
         </is>
       </c>
       <c r="H279" s="18" t="n">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="I279" s="18" t="inlineStr">
         <is>
@@ -31085,7 +31085,7 @@
         </is>
       </c>
       <c r="H280" s="17" t="n">
-        <v>0.39</v>
+        <v>0.42</v>
       </c>
       <c r="I280" s="17" t="inlineStr">
         <is>
@@ -31135,7 +31135,7 @@
         </is>
       </c>
       <c r="H281" s="18" t="n">
-        <v>0.43</v>
+        <v>0.26</v>
       </c>
       <c r="I281" s="18" t="inlineStr">
         <is>
@@ -31185,7 +31185,7 @@
         </is>
       </c>
       <c r="H282" s="17" t="n">
-        <v>0.26</v>
+        <v>0.12</v>
       </c>
       <c r="I282" s="17" t="inlineStr">
         <is>
@@ -31235,7 +31235,7 @@
         </is>
       </c>
       <c r="H283" s="18" t="n">
-        <v>0.21</v>
+        <v>0.19</v>
       </c>
       <c r="I283" s="18" t="inlineStr">
         <is>
@@ -31285,7 +31285,7 @@
         </is>
       </c>
       <c r="H284" s="17" t="n">
-        <v>0.27</v>
+        <v>0.13</v>
       </c>
       <c r="I284" s="17" t="inlineStr">
         <is>
@@ -31335,7 +31335,7 @@
         </is>
       </c>
       <c r="H285" s="18" t="n">
-        <v>0.38</v>
+        <v>0.23</v>
       </c>
       <c r="I285" s="18" t="inlineStr">
         <is>
@@ -31385,7 +31385,7 @@
         </is>
       </c>
       <c r="H286" s="17" t="n">
-        <v>0.18</v>
+        <v>0.37</v>
       </c>
       <c r="I286" s="17" t="inlineStr">
         <is>
@@ -31435,7 +31435,7 @@
         </is>
       </c>
       <c r="H287" s="18" t="n">
-        <v>0.35</v>
+        <v>0.31</v>
       </c>
       <c r="I287" s="18" t="inlineStr">
         <is>
@@ -31485,7 +31485,7 @@
         </is>
       </c>
       <c r="H288" s="17" t="n">
-        <v>0.42</v>
+        <v>0.26</v>
       </c>
       <c r="I288" s="17" t="inlineStr">
         <is>
@@ -31535,7 +31535,7 @@
         </is>
       </c>
       <c r="H289" s="18" t="n">
-        <v>0.22</v>
+        <v>0.4</v>
       </c>
       <c r="I289" s="18" t="inlineStr">
         <is>
@@ -31585,7 +31585,7 @@
         </is>
       </c>
       <c r="H290" s="17" t="n">
-        <v>0.32</v>
+        <v>0.4</v>
       </c>
       <c r="I290" s="17" t="inlineStr">
         <is>
@@ -31635,7 +31635,7 @@
         </is>
       </c>
       <c r="H291" s="18" t="n">
-        <v>0.24</v>
+        <v>0.44</v>
       </c>
       <c r="I291" s="18" t="inlineStr">
         <is>
@@ -31685,7 +31685,7 @@
         </is>
       </c>
       <c r="H292" s="17" t="n">
-        <v>0.19</v>
+        <v>0.42</v>
       </c>
       <c r="I292" s="17" t="inlineStr">
         <is>
@@ -31735,7 +31735,7 @@
         </is>
       </c>
       <c r="H293" s="18" t="n">
-        <v>0.34</v>
+        <v>0.37</v>
       </c>
       <c r="I293" s="18" t="inlineStr">
         <is>
@@ -31785,7 +31785,7 @@
         </is>
       </c>
       <c r="H294" s="17" t="n">
-        <v>0.15</v>
+        <v>0.25</v>
       </c>
       <c r="I294" s="17" t="inlineStr">
         <is>
@@ -31835,7 +31835,7 @@
         </is>
       </c>
       <c r="H295" s="18" t="n">
-        <v>0.12</v>
+        <v>0.33</v>
       </c>
       <c r="I295" s="18" t="inlineStr">
         <is>
@@ -31885,7 +31885,7 @@
         </is>
       </c>
       <c r="H296" s="17" t="n">
-        <v>0.13</v>
+        <v>0.44</v>
       </c>
       <c r="I296" s="17" t="inlineStr">
         <is>
@@ -31935,7 +31935,7 @@
         </is>
       </c>
       <c r="H297" s="18" t="n">
-        <v>0.25</v>
+        <v>0.11</v>
       </c>
       <c r="I297" s="18" t="inlineStr">
         <is>
@@ -31985,7 +31985,7 @@
         </is>
       </c>
       <c r="H298" s="17" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="I298" s="17" t="inlineStr">
         <is>
@@ -32035,7 +32035,7 @@
         </is>
       </c>
       <c r="H299" s="18" t="n">
-        <v>0.4</v>
+        <v>0.22</v>
       </c>
       <c r="I299" s="18" t="inlineStr">
         <is>
@@ -32135,7 +32135,7 @@
         </is>
       </c>
       <c r="H301" s="18" t="n">
-        <v>0.28</v>
+        <v>0.3</v>
       </c>
       <c r="I301" s="18" t="inlineStr">
         <is>
@@ -32185,7 +32185,7 @@
         </is>
       </c>
       <c r="H302" s="17" t="n">
-        <v>0.33</v>
+        <v>0.44</v>
       </c>
       <c r="I302" s="17" t="inlineStr">
         <is>
@@ -32235,7 +32235,7 @@
         </is>
       </c>
       <c r="H303" s="18" t="n">
-        <v>0.27</v>
+        <v>0.41</v>
       </c>
       <c r="I303" s="18" t="inlineStr">
         <is>
@@ -32285,7 +32285,7 @@
         </is>
       </c>
       <c r="H304" s="17" t="n">
-        <v>0.16</v>
+        <v>0.32</v>
       </c>
       <c r="I304" s="17" t="inlineStr">
         <is>
@@ -32335,7 +32335,7 @@
         </is>
       </c>
       <c r="H305" s="18" t="n">
-        <v>0.44</v>
+        <v>0.42</v>
       </c>
       <c r="I305" s="18" t="inlineStr">
         <is>
@@ -32385,7 +32385,7 @@
         </is>
       </c>
       <c r="H306" s="17" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="I306" s="17" t="inlineStr">
         <is>
@@ -32435,7 +32435,7 @@
         </is>
       </c>
       <c r="H307" s="18" t="n">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="I307" s="18" t="inlineStr">
         <is>
@@ -32485,7 +32485,7 @@
         </is>
       </c>
       <c r="H308" s="17" t="n">
-        <v>0.08</v>
+        <v>0.42</v>
       </c>
       <c r="I308" s="17" t="inlineStr">
         <is>
@@ -32535,7 +32535,7 @@
         </is>
       </c>
       <c r="H309" s="18" t="n">
-        <v>0.18</v>
+        <v>0.39</v>
       </c>
       <c r="I309" s="18" t="inlineStr">
         <is>
@@ -32585,7 +32585,7 @@
         </is>
       </c>
       <c r="H310" s="17" t="n">
-        <v>0.35</v>
+        <v>0.31</v>
       </c>
       <c r="I310" s="17" t="inlineStr">
         <is>
@@ -32635,7 +32635,7 @@
         </is>
       </c>
       <c r="H311" s="18" t="n">
-        <v>0.2</v>
+        <v>0.26</v>
       </c>
       <c r="I311" s="18" t="inlineStr">
         <is>
@@ -32685,7 +32685,7 @@
         </is>
       </c>
       <c r="H312" s="17" t="n">
-        <v>0.05</v>
+        <v>0.26</v>
       </c>
       <c r="I312" s="17" t="inlineStr">
         <is>
@@ -32735,7 +32735,7 @@
         </is>
       </c>
       <c r="H313" s="18" t="n">
-        <v>0.39</v>
+        <v>0.16</v>
       </c>
       <c r="I313" s="18" t="inlineStr">
         <is>
@@ -32785,7 +32785,7 @@
         </is>
       </c>
       <c r="H314" s="17" t="n">
-        <v>0.06</v>
+        <v>0.15</v>
       </c>
       <c r="I314" s="17" t="inlineStr">
         <is>
@@ -32835,7 +32835,7 @@
         </is>
       </c>
       <c r="H315" s="18" t="n">
-        <v>0.11</v>
+        <v>0.19</v>
       </c>
       <c r="I315" s="18" t="inlineStr">
         <is>
@@ -32885,7 +32885,7 @@
         </is>
       </c>
       <c r="H316" s="17" t="n">
-        <v>0.06</v>
+        <v>0.3</v>
       </c>
       <c r="I316" s="17" t="inlineStr">
         <is>
@@ -32935,7 +32935,7 @@
         </is>
       </c>
       <c r="H317" s="18" t="n">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="I317" s="18" t="inlineStr">
         <is>
@@ -32985,7 +32985,7 @@
         </is>
       </c>
       <c r="H318" s="17" t="n">
-        <v>0.08</v>
+        <v>0.36</v>
       </c>
       <c r="I318" s="17" t="inlineStr">
         <is>
@@ -33035,7 +33035,7 @@
         </is>
       </c>
       <c r="H319" s="18" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.31</v>
       </c>
       <c r="I319" s="18" t="inlineStr">
         <is>
@@ -33085,7 +33085,7 @@
         </is>
       </c>
       <c r="H320" s="17" t="n">
-        <v>0.43</v>
+        <v>0.3</v>
       </c>
       <c r="I320" s="17" t="inlineStr">
         <is>
@@ -33135,7 +33135,7 @@
         </is>
       </c>
       <c r="H321" s="18" t="n">
-        <v>0.25</v>
+        <v>0.27</v>
       </c>
       <c r="I321" s="18" t="inlineStr">
         <is>
@@ -33185,7 +33185,7 @@
         </is>
       </c>
       <c r="H322" s="17" t="n">
-        <v>0.37</v>
+        <v>0.4</v>
       </c>
       <c r="I322" s="17" t="inlineStr">
         <is>
@@ -33235,7 +33235,7 @@
         </is>
       </c>
       <c r="H323" s="18" t="n">
-        <v>0.11</v>
+        <v>0.28</v>
       </c>
       <c r="I323" s="18" t="inlineStr">
         <is>
@@ -33285,7 +33285,7 @@
         </is>
       </c>
       <c r="H324" s="17" t="n">
-        <v>0.3</v>
+        <v>0.16</v>
       </c>
       <c r="I324" s="17" t="inlineStr">
         <is>
@@ -33335,7 +33335,7 @@
         </is>
       </c>
       <c r="H325" s="18" t="n">
-        <v>0.35</v>
+        <v>0.34</v>
       </c>
       <c r="I325" s="18" t="inlineStr">
         <is>
@@ -33430,7 +33430,7 @@
         </is>
       </c>
       <c r="E2" s="17" t="n">
-        <v>0.16</v>
+        <v>0.24</v>
       </c>
       <c r="F2" s="17" t="inlineStr">
         <is>
